--- a/procurement_documents/delivery_attachment.xlsx
+++ b/procurement_documents/delivery_attachment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emman\OneDrive\Desktop\Thesis Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emman\itrac\procurement_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B736E8-4040-40E9-8513-3E8093C6EA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E9B10D-F087-478B-BCD8-8E7218D1BD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAR" sheetId="2" r:id="rId1"/>
@@ -876,18 +876,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1371,9 +1365,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1399,25 +1390,25 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="41" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="41" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1474,7 +1465,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="27" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1541,7 +1532,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1550,10 +1541,10 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1614,13 +1605,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="41" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="41" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1677,11 +1668,11 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1801,10 +1792,10 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="49" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1878,25 +1869,466 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1908,464 +2340,119 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="50" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2379,100 +2466,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3229,109 +3223,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="341"/>
-      <c r="B1" s="341"/>
-      <c r="C1" s="341"/>
-      <c r="D1" s="342"/>
-      <c r="E1" s="342"/>
-      <c r="F1" s="342"/>
+      <c r="A1" s="358"/>
+      <c r="B1" s="358"/>
+      <c r="C1" s="358"/>
+      <c r="D1" s="359"/>
+      <c r="E1" s="359"/>
+      <c r="F1" s="359"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
-      <c r="A2" s="343" t="s">
+      <c r="A2" s="360" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="344"/>
-      <c r="C2" s="344"/>
-      <c r="D2" s="345" t="s">
+      <c r="B2" s="361"/>
+      <c r="C2" s="361"/>
+      <c r="D2" s="362" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="345"/>
-      <c r="F2" s="345"/>
+      <c r="E2" s="362"/>
+      <c r="F2" s="362"/>
     </row>
     <row r="3" spans="1:6" ht="18.75">
-      <c r="A3" s="346" t="s">
+      <c r="A3" s="363" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="346"/>
-      <c r="C3" s="346"/>
-      <c r="D3" s="345" t="s">
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="362" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="345"/>
-      <c r="F3" s="345"/>
+      <c r="E3" s="362"/>
+      <c r="F3" s="362"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="347" t="s">
+      <c r="A4" s="364" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="347"/>
-      <c r="C4" s="347"/>
-      <c r="D4" s="345" t="s">
+      <c r="B4" s="364"/>
+      <c r="C4" s="364"/>
+      <c r="D4" s="362" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="345"/>
-      <c r="F4" s="345"/>
+      <c r="E4" s="362"/>
+      <c r="F4" s="362"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="347" t="s">
+      <c r="A5" s="364" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="347"/>
-      <c r="C5" s="347"/>
-      <c r="D5" s="348" t="s">
+      <c r="B5" s="364"/>
+      <c r="C5" s="364"/>
+      <c r="D5" s="365" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="348"/>
-      <c r="F5" s="348"/>
+      <c r="E5" s="365"/>
+      <c r="F5" s="365"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="349" t="s">
+      <c r="A6" s="366" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="349"/>
-      <c r="C6" s="349"/>
-      <c r="D6" s="350"/>
-      <c r="E6" s="350"/>
-      <c r="F6" s="350"/>
+      <c r="B6" s="366"/>
+      <c r="C6" s="366"/>
+      <c r="D6" s="367"/>
+      <c r="E6" s="367"/>
+      <c r="F6" s="367"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="325" t="s">
+      <c r="A7" s="368" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="326"/>
+      <c r="B7" s="369"/>
       <c r="C7" s="39"/>
       <c r="D7" s="33"/>
-      <c r="E7" s="115" t="s">
+      <c r="E7" s="114" t="s">
         <v>127</v>
       </c>
       <c r="F7" s="38"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="325" t="s">
+      <c r="A8" s="368" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="326"/>
+      <c r="B8" s="369"/>
       <c r="C8" s="40"/>
       <c r="D8" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="234"/>
-      <c r="F8" s="114"/>
+      <c r="E8" s="233"/>
+      <c r="F8" s="499"/>
     </row>
     <row r="9" spans="1:6" ht="30">
-      <c r="A9" s="235" t="s">
+      <c r="A9" s="234" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="235" t="s">
+      <c r="B9" s="234" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="235" t="s">
+      <c r="C9" s="234" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="236" t="s">
+      <c r="D9" s="235" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="238" t="s">
+      <c r="E9" s="237" t="s">
         <v>32</v>
       </c>
       <c r="F9" s="35" t="s">
@@ -3342,364 +3336,379 @@
       <c r="A10" s="81"/>
       <c r="B10" s="81"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="209"/>
-      <c r="E10" s="184"/>
-      <c r="F10" s="196"/>
+      <c r="D10" s="208"/>
+      <c r="E10" s="183"/>
+      <c r="F10" s="195"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="234"/>
-      <c r="B11" s="234"/>
-      <c r="C11" s="222"/>
-      <c r="D11" s="183"/>
-      <c r="E11" s="184"/>
-      <c r="F11" s="196"/>
+      <c r="A11" s="233"/>
+      <c r="B11" s="233"/>
+      <c r="C11" s="221"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="195"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="233"/>
-      <c r="B12" s="233"/>
-      <c r="C12" s="137"/>
-      <c r="D12" s="204"/>
+      <c r="A12" s="232"/>
+      <c r="B12" s="232"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="203"/>
       <c r="E12" s="58"/>
       <c r="F12" s="88"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="233"/>
-      <c r="B13" s="233"/>
+      <c r="A13" s="232"/>
+      <c r="B13" s="232"/>
       <c r="C13" s="101"/>
-      <c r="D13" s="205"/>
-      <c r="E13" s="184"/>
-      <c r="F13" s="185"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="183"/>
+      <c r="F13" s="184"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="233"/>
-      <c r="B14" s="233"/>
-      <c r="C14" s="232"/>
-      <c r="D14" s="208"/>
+      <c r="A14" s="232"/>
+      <c r="B14" s="232"/>
+      <c r="C14" s="231"/>
+      <c r="D14" s="207"/>
       <c r="E14" s="58"/>
       <c r="F14" s="88"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="182"/>
-      <c r="B15" s="182"/>
+      <c r="A15" s="181"/>
+      <c r="B15" s="181"/>
       <c r="C15" s="102"/>
-      <c r="D15" s="204"/>
-      <c r="E15" s="184"/>
-      <c r="F15" s="185"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="184"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="182"/>
-      <c r="B16" s="182"/>
+      <c r="A16" s="181"/>
+      <c r="B16" s="181"/>
       <c r="C16" s="11"/>
       <c r="D16" s="91"/>
       <c r="E16" s="20"/>
       <c r="F16" s="88"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="182"/>
-      <c r="B17" s="182"/>
+      <c r="A17" s="181"/>
+      <c r="B17" s="181"/>
       <c r="C17" s="102"/>
       <c r="D17" s="92"/>
       <c r="E17" s="20"/>
       <c r="F17" s="88"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="182"/>
-      <c r="B18" s="182"/>
+      <c r="A18" s="181"/>
+      <c r="B18" s="181"/>
       <c r="C18" s="101"/>
-      <c r="D18" s="206"/>
+      <c r="D18" s="205"/>
       <c r="E18" s="20"/>
-      <c r="F18" s="185"/>
+      <c r="F18" s="184"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="182"/>
-      <c r="B19" s="182"/>
+      <c r="A19" s="181"/>
+      <c r="B19" s="181"/>
       <c r="C19" s="102"/>
-      <c r="D19" s="204"/>
-      <c r="E19" s="184"/>
-      <c r="F19" s="185"/>
+      <c r="D19" s="203"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="184"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="182"/>
-      <c r="B20" s="182"/>
+      <c r="A20" s="181"/>
+      <c r="B20" s="181"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="204"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="185"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="183"/>
+      <c r="F20" s="184"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="182"/>
-      <c r="B21" s="182"/>
+      <c r="A21" s="181"/>
+      <c r="B21" s="181"/>
       <c r="C21" s="101"/>
-      <c r="D21" s="205"/>
+      <c r="D21" s="204"/>
       <c r="E21" s="20"/>
-      <c r="F21" s="185"/>
+      <c r="F21" s="184"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="233"/>
-      <c r="B22" s="233"/>
+      <c r="A22" s="232"/>
+      <c r="B22" s="232"/>
       <c r="C22" s="11"/>
       <c r="D22" s="90"/>
       <c r="E22" s="58"/>
       <c r="F22" s="88"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="233"/>
-      <c r="B23" s="233"/>
-      <c r="C23" s="239"/>
+      <c r="A23" s="232"/>
+      <c r="B23" s="232"/>
+      <c r="C23" s="238"/>
       <c r="D23" s="89"/>
       <c r="E23" s="20"/>
       <c r="F23" s="88"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="233"/>
-      <c r="B24" s="233"/>
-      <c r="C24" s="237"/>
+      <c r="A24" s="232"/>
+      <c r="B24" s="232"/>
+      <c r="C24" s="236"/>
       <c r="D24" s="89"/>
       <c r="E24" s="20"/>
       <c r="F24" s="88"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="233"/>
-      <c r="B25" s="233"/>
+      <c r="A25" s="232"/>
+      <c r="B25" s="232"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="224"/>
-      <c r="E25" s="184"/>
-      <c r="F25" s="185"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="183"/>
+      <c r="F25" s="184"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="233"/>
-      <c r="B26" s="233"/>
+      <c r="A26" s="232"/>
+      <c r="B26" s="232"/>
       <c r="C26" s="109"/>
       <c r="D26" s="89"/>
       <c r="E26" s="20"/>
       <c r="F26" s="88"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="233"/>
-      <c r="B27" s="233"/>
+      <c r="A27" s="232"/>
+      <c r="B27" s="232"/>
       <c r="C27" s="102"/>
       <c r="D27" s="89"/>
       <c r="E27" s="20"/>
       <c r="F27" s="88"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="233"/>
-      <c r="B28" s="233"/>
-      <c r="C28" s="223"/>
+      <c r="A28" s="232"/>
+      <c r="B28" s="232"/>
+      <c r="C28" s="222"/>
       <c r="D28" s="89"/>
       <c r="E28" s="20"/>
       <c r="F28" s="88"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="233"/>
-      <c r="B29" s="233"/>
-      <c r="C29" s="232"/>
+      <c r="A29" s="232"/>
+      <c r="B29" s="232"/>
+      <c r="C29" s="231"/>
       <c r="D29" s="89"/>
       <c r="E29" s="20"/>
       <c r="F29" s="88"/>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="233"/>
-      <c r="B30" s="233"/>
+      <c r="A30" s="232"/>
+      <c r="B30" s="232"/>
       <c r="C30" s="112"/>
       <c r="D30" s="89"/>
       <c r="E30" s="20"/>
       <c r="F30" s="88"/>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="233"/>
-      <c r="B31" s="233"/>
+      <c r="A31" s="232"/>
+      <c r="B31" s="232"/>
       <c r="C31" s="57"/>
       <c r="D31" s="89"/>
       <c r="E31" s="20"/>
       <c r="F31" s="88"/>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="233"/>
-      <c r="B32" s="233"/>
+      <c r="A32" s="232"/>
+      <c r="B32" s="232"/>
       <c r="C32" s="113"/>
       <c r="D32" s="89"/>
       <c r="E32" s="20"/>
       <c r="F32" s="88"/>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="233"/>
-      <c r="B33" s="233"/>
+      <c r="A33" s="232"/>
+      <c r="B33" s="232"/>
       <c r="C33" s="57"/>
       <c r="D33" s="89"/>
       <c r="E33" s="20"/>
       <c r="F33" s="88"/>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="233"/>
-      <c r="B34" s="233"/>
+      <c r="A34" s="232"/>
+      <c r="B34" s="232"/>
       <c r="C34" s="57"/>
       <c r="D34" s="95"/>
       <c r="E34" s="20"/>
       <c r="F34" s="88"/>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="233"/>
-      <c r="B35" s="233"/>
-      <c r="C35" s="237"/>
+      <c r="A35" s="232"/>
+      <c r="B35" s="232"/>
+      <c r="C35" s="236"/>
       <c r="D35" s="89"/>
       <c r="E35" s="20"/>
       <c r="F35" s="88"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="233"/>
-      <c r="B36" s="233"/>
+      <c r="A36" s="232"/>
+      <c r="B36" s="232"/>
       <c r="C36" s="109"/>
       <c r="D36" s="89"/>
       <c r="E36" s="20"/>
       <c r="F36" s="88"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="233"/>
-      <c r="B37" s="233"/>
+      <c r="A37" s="232"/>
+      <c r="B37" s="232"/>
       <c r="C37" s="109"/>
       <c r="D37" s="89"/>
       <c r="E37" s="20"/>
       <c r="F37" s="88"/>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="233"/>
-      <c r="B38" s="233"/>
+      <c r="A38" s="232"/>
+      <c r="B38" s="232"/>
       <c r="C38" s="109"/>
       <c r="D38" s="89"/>
       <c r="E38" s="20"/>
       <c r="F38" s="88"/>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="233"/>
-      <c r="B39" s="233"/>
-      <c r="C39" s="237"/>
+      <c r="A39" s="232"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="236"/>
       <c r="D39" s="89"/>
       <c r="E39" s="20"/>
       <c r="F39" s="88"/>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="233"/>
-      <c r="B40" s="233"/>
+      <c r="A40" s="232"/>
+      <c r="B40" s="232"/>
       <c r="C40" s="80"/>
       <c r="D40" s="89"/>
       <c r="E40" s="52"/>
       <c r="F40" s="87"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="233"/>
-      <c r="B41" s="233"/>
-      <c r="C41" s="237"/>
+      <c r="A41" s="232"/>
+      <c r="B41" s="232"/>
+      <c r="C41" s="236"/>
       <c r="D41" s="89"/>
       <c r="E41" s="20"/>
       <c r="F41" s="87"/>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="233"/>
-      <c r="B42" s="233"/>
+      <c r="A42" s="232"/>
+      <c r="B42" s="232"/>
       <c r="C42" s="80"/>
       <c r="D42" s="89"/>
       <c r="E42" s="20"/>
       <c r="F42" s="87"/>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="233"/>
-      <c r="B43" s="233"/>
+      <c r="A43" s="232"/>
+      <c r="B43" s="232"/>
       <c r="C43" s="80"/>
       <c r="D43" s="96"/>
       <c r="E43" s="97"/>
       <c r="F43" s="98"/>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="336" t="s">
+      <c r="A44" s="370" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="337"/>
+      <c r="B44" s="371"/>
       <c r="C44" s="36"/>
-      <c r="D44" s="231" t="s">
+      <c r="D44" s="230" t="s">
         <v>33</v>
       </c>
       <c r="E44" s="24"/>
       <c r="F44" s="37"/>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="330"/>
-      <c r="B45" s="331"/>
-      <c r="C45" s="332"/>
-      <c r="D45" s="330"/>
-      <c r="E45" s="331"/>
-      <c r="F45" s="332"/>
+      <c r="A45" s="301"/>
+      <c r="B45" s="302"/>
+      <c r="C45" s="308"/>
+      <c r="D45" s="301"/>
+      <c r="E45" s="302"/>
+      <c r="F45" s="308"/>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="330"/>
-      <c r="B46" s="331"/>
-      <c r="C46" s="332"/>
-      <c r="D46" s="330"/>
-      <c r="E46" s="331"/>
-      <c r="F46" s="332"/>
+      <c r="A46" s="301"/>
+      <c r="B46" s="302"/>
+      <c r="C46" s="308"/>
+      <c r="D46" s="301"/>
+      <c r="E46" s="302"/>
+      <c r="F46" s="308"/>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="327"/>
-      <c r="B47" s="328"/>
-      <c r="C47" s="329"/>
-      <c r="D47" s="327" t="s">
+      <c r="A47" s="313"/>
+      <c r="B47" s="314"/>
+      <c r="C47" s="315"/>
+      <c r="D47" s="313" t="s">
         <v>128</v>
       </c>
-      <c r="E47" s="328"/>
-      <c r="F47" s="329"/>
+      <c r="E47" s="314"/>
+      <c r="F47" s="315"/>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="330" t="s">
+      <c r="A48" s="301" t="s">
         <v>23</v>
       </c>
-      <c r="B48" s="331"/>
-      <c r="C48" s="332"/>
-      <c r="D48" s="330" t="s">
+      <c r="B48" s="302"/>
+      <c r="C48" s="308"/>
+      <c r="D48" s="301" t="s">
         <v>34</v>
       </c>
-      <c r="E48" s="331"/>
-      <c r="F48" s="332"/>
+      <c r="E48" s="302"/>
+      <c r="F48" s="308"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="327"/>
-      <c r="B49" s="328"/>
-      <c r="C49" s="329"/>
-      <c r="D49" s="330"/>
-      <c r="E49" s="331"/>
-      <c r="F49" s="332"/>
+      <c r="A49" s="313"/>
+      <c r="B49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="301"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="308"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="330" t="s">
+      <c r="A50" s="301" t="s">
         <v>24</v>
       </c>
-      <c r="B50" s="331"/>
-      <c r="C50" s="332"/>
-      <c r="D50" s="333"/>
-      <c r="E50" s="334"/>
-      <c r="F50" s="335"/>
+      <c r="B50" s="302"/>
+      <c r="C50" s="308"/>
+      <c r="D50" s="351"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="333"/>
-      <c r="B51" s="334"/>
-      <c r="C51" s="335"/>
-      <c r="D51" s="330" t="s">
+      <c r="A51" s="351"/>
+      <c r="B51" s="356"/>
+      <c r="C51" s="357"/>
+      <c r="D51" s="301" t="s">
         <v>25</v>
       </c>
-      <c r="E51" s="331"/>
-      <c r="F51" s="332"/>
+      <c r="E51" s="302"/>
+      <c r="F51" s="308"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="338" t="s">
+      <c r="A52" s="326" t="s">
         <v>25</v>
       </c>
-      <c r="B52" s="339"/>
-      <c r="C52" s="340"/>
-      <c r="D52" s="338"/>
-      <c r="E52" s="339"/>
-      <c r="F52" s="340"/>
+      <c r="B52" s="327"/>
+      <c r="C52" s="328"/>
+      <c r="D52" s="326"/>
+      <c r="E52" s="327"/>
+      <c r="F52" s="328"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:F45"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="A51:C51"/>
@@ -3716,21 +3725,6 @@
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:F45"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3752,469 +3746,469 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="352"/>
-      <c r="B1" s="353"/>
-      <c r="C1" s="353"/>
-      <c r="D1" s="354"/>
-      <c r="E1" s="355"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="357"/>
+      <c r="A1" s="403"/>
+      <c r="B1" s="404"/>
+      <c r="C1" s="404"/>
+      <c r="D1" s="405"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="333"/>
+      <c r="G1" s="333"/>
+      <c r="H1" s="333"/>
+      <c r="I1" s="334"/>
     </row>
     <row r="2" spans="1:9" ht="15.75">
-      <c r="A2" s="358" t="s">
+      <c r="A2" s="406" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="360"/>
-      <c r="E2" s="361"/>
-      <c r="F2" s="362"/>
-      <c r="G2" s="362"/>
-      <c r="H2" s="362"/>
-      <c r="I2" s="363"/>
+      <c r="B2" s="407"/>
+      <c r="C2" s="407"/>
+      <c r="D2" s="408"/>
+      <c r="E2" s="409"/>
+      <c r="F2" s="410"/>
+      <c r="G2" s="410"/>
+      <c r="H2" s="410"/>
+      <c r="I2" s="411"/>
     </row>
     <row r="3" spans="1:9" ht="17.25">
-      <c r="A3" s="358" t="s">
+      <c r="A3" s="406" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="360"/>
-      <c r="E3" s="364" t="s">
+      <c r="B3" s="407"/>
+      <c r="C3" s="407"/>
+      <c r="D3" s="408"/>
+      <c r="E3" s="412" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="366"/>
+      <c r="F3" s="413"/>
+      <c r="G3" s="413"/>
+      <c r="H3" s="413"/>
+      <c r="I3" s="414"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="367" t="s">
+      <c r="A4" s="415" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="368"/>
-      <c r="C4" s="368"/>
-      <c r="D4" s="369"/>
-      <c r="E4" s="370" t="s">
+      <c r="B4" s="416"/>
+      <c r="C4" s="416"/>
+      <c r="D4" s="417"/>
+      <c r="E4" s="341" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="371"/>
-      <c r="G4" s="371"/>
-      <c r="H4" s="371"/>
-      <c r="I4" s="372"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="343"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="367" t="s">
+      <c r="A5" s="415" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="368"/>
-      <c r="C5" s="368"/>
-      <c r="D5" s="369"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="371"/>
-      <c r="G5" s="371"/>
-      <c r="H5" s="371"/>
-      <c r="I5" s="372"/>
+      <c r="B5" s="416"/>
+      <c r="C5" s="416"/>
+      <c r="D5" s="417"/>
+      <c r="E5" s="341"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="343"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="373" t="s">
+      <c r="A6" s="418" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="374"/>
-      <c r="C6" s="374"/>
-      <c r="D6" s="375"/>
-      <c r="E6" s="376"/>
-      <c r="F6" s="377"/>
-      <c r="G6" s="377"/>
-      <c r="H6" s="377"/>
-      <c r="I6" s="378"/>
+      <c r="B6" s="419"/>
+      <c r="C6" s="419"/>
+      <c r="D6" s="420"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="345"/>
+      <c r="G6" s="345"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="346"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="379" t="s">
+      <c r="A7" s="421" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="380"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="285" t="s">
+      <c r="B7" s="422"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="284" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
       <c r="H7" s="17"/>
-      <c r="I7" s="122"/>
+      <c r="I7" s="121"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="381"/>
-      <c r="C8" s="381"/>
-      <c r="D8" s="382"/>
+      <c r="B8" s="423"/>
+      <c r="C8" s="423"/>
+      <c r="D8" s="319"/>
       <c r="E8" s="15" t="s">
         <v>92</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="116"/>
+      <c r="I8" s="115"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="381"/>
-      <c r="C9" s="381"/>
-      <c r="D9" s="382"/>
+      <c r="B9" s="423"/>
+      <c r="C9" s="423"/>
+      <c r="D9" s="319"/>
       <c r="E9" s="15" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="389"/>
-      <c r="H9" s="389"/>
-      <c r="I9" s="390"/>
+      <c r="G9" s="395"/>
+      <c r="H9" s="395"/>
+      <c r="I9" s="396"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="391" t="s">
+      <c r="A10" s="397" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="392"/>
-      <c r="C10" s="392"/>
-      <c r="D10" s="392"/>
-      <c r="E10" s="393"/>
-      <c r="F10" s="394" t="s">
+      <c r="B10" s="398"/>
+      <c r="C10" s="398"/>
+      <c r="D10" s="398"/>
+      <c r="E10" s="399"/>
+      <c r="F10" s="400" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="395"/>
-      <c r="H10" s="391" t="s">
+      <c r="G10" s="401"/>
+      <c r="H10" s="397" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="393"/>
+      <c r="I10" s="399"/>
     </row>
     <row r="11" spans="1:9" ht="30">
       <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="287" t="s">
+      <c r="B11" s="286" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="396" t="s">
+      <c r="C11" s="377" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="397"/>
-      <c r="E11" s="287" t="s">
+      <c r="D11" s="378"/>
+      <c r="E11" s="286" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="287" t="s">
+      <c r="F11" s="286" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="287" t="s">
+      <c r="G11" s="286" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="287" t="s">
+      <c r="H11" s="286" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="287" t="s">
+      <c r="I11" s="286" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="13.7" customHeight="1">
       <c r="A12" s="6"/>
-      <c r="B12" s="221"/>
+      <c r="B12" s="220"/>
       <c r="C12" s="8"/>
       <c r="D12" s="104"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="221"/>
+      <c r="E12" s="212"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="220"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" ht="13.7" customHeight="1">
       <c r="A13" s="6"/>
-      <c r="B13" s="221"/>
+      <c r="B13" s="220"/>
       <c r="C13" s="8"/>
       <c r="D13" s="104"/>
-      <c r="E13" s="214"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="221"/>
-      <c r="I13" s="287"/>
+      <c r="E13" s="213"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="123"/>
+      <c r="H13" s="220"/>
+      <c r="I13" s="286"/>
     </row>
     <row r="14" spans="1:9" ht="13.7" customHeight="1">
       <c r="A14" s="6"/>
-      <c r="B14" s="221"/>
-      <c r="C14" s="268"/>
-      <c r="D14" s="276"/>
-      <c r="E14" s="214"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="210"/>
-      <c r="I14" s="287"/>
+      <c r="B14" s="220"/>
+      <c r="C14" s="267"/>
+      <c r="D14" s="275"/>
+      <c r="E14" s="213"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="123"/>
+      <c r="H14" s="209"/>
+      <c r="I14" s="286"/>
     </row>
     <row r="15" spans="1:9" ht="13.7" customHeight="1">
       <c r="A15" s="6"/>
-      <c r="B15" s="221"/>
-      <c r="C15" s="297"/>
-      <c r="D15" s="286"/>
-      <c r="E15" s="215"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="221"/>
-      <c r="I15" s="287"/>
+      <c r="B15" s="220"/>
+      <c r="C15" s="296"/>
+      <c r="D15" s="285"/>
+      <c r="E15" s="214"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="123"/>
+      <c r="H15" s="220"/>
+      <c r="I15" s="286"/>
     </row>
     <row r="16" spans="1:9" ht="13.7" customHeight="1">
       <c r="A16" s="6"/>
-      <c r="B16" s="221"/>
-      <c r="C16" s="268"/>
-      <c r="D16" s="276"/>
-      <c r="E16" s="215"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="228"/>
-      <c r="I16" s="287"/>
+      <c r="B16" s="220"/>
+      <c r="C16" s="267"/>
+      <c r="D16" s="275"/>
+      <c r="E16" s="214"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="227"/>
+      <c r="I16" s="286"/>
     </row>
     <row r="17" spans="1:9" ht="13.7" customHeight="1">
       <c r="A17" s="6"/>
-      <c r="B17" s="221"/>
-      <c r="C17" s="275"/>
-      <c r="D17" s="276"/>
-      <c r="E17" s="215"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="228"/>
-      <c r="I17" s="287"/>
+      <c r="B17" s="220"/>
+      <c r="C17" s="274"/>
+      <c r="D17" s="275"/>
+      <c r="E17" s="214"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="123"/>
+      <c r="H17" s="227"/>
+      <c r="I17" s="286"/>
     </row>
     <row r="18" spans="1:9" ht="13.7" customHeight="1">
       <c r="A18" s="6"/>
-      <c r="B18" s="221"/>
-      <c r="C18" s="403"/>
-      <c r="D18" s="404"/>
-      <c r="E18" s="215"/>
-      <c r="F18" s="126"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="228"/>
-      <c r="I18" s="287"/>
+      <c r="B18" s="220"/>
+      <c r="C18" s="311"/>
+      <c r="D18" s="312"/>
+      <c r="E18" s="214"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="227"/>
+      <c r="I18" s="286"/>
     </row>
     <row r="19" spans="1:9" ht="13.7" customHeight="1">
       <c r="A19" s="52"/>
-      <c r="B19" s="221"/>
-      <c r="C19" s="219"/>
+      <c r="B19" s="220"/>
+      <c r="C19" s="218"/>
       <c r="D19" s="105"/>
-      <c r="E19" s="216"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="228"/>
+      <c r="E19" s="215"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="227"/>
       <c r="I19" s="52"/>
     </row>
     <row r="20" spans="1:9" ht="13.7" customHeight="1">
       <c r="A20" s="52"/>
-      <c r="B20" s="221"/>
-      <c r="C20" s="403"/>
-      <c r="D20" s="404"/>
-      <c r="E20" s="216"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="272"/>
+      <c r="B20" s="220"/>
+      <c r="C20" s="311"/>
+      <c r="D20" s="312"/>
+      <c r="E20" s="215"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="271"/>
       <c r="I20" s="52"/>
     </row>
     <row r="21" spans="1:9" ht="13.7" customHeight="1">
       <c r="A21" s="52"/>
-      <c r="B21" s="221"/>
-      <c r="C21" s="219"/>
-      <c r="D21" s="229"/>
-      <c r="E21" s="216"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="124"/>
-      <c r="H21" s="228"/>
+      <c r="B21" s="220"/>
+      <c r="C21" s="218"/>
+      <c r="D21" s="228"/>
+      <c r="E21" s="215"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="227"/>
       <c r="I21" s="52"/>
     </row>
     <row r="22" spans="1:9" ht="13.7" customHeight="1">
-      <c r="A22" s="200"/>
-      <c r="B22" s="221"/>
-      <c r="C22" s="268"/>
-      <c r="D22" s="269"/>
-      <c r="E22" s="217"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="221"/>
-      <c r="I22" s="200"/>
+      <c r="A22" s="199"/>
+      <c r="B22" s="220"/>
+      <c r="C22" s="267"/>
+      <c r="D22" s="268"/>
+      <c r="E22" s="216"/>
+      <c r="F22" s="202"/>
+      <c r="G22" s="201"/>
+      <c r="H22" s="220"/>
+      <c r="I22" s="199"/>
     </row>
     <row r="23" spans="1:9" ht="13.7" customHeight="1">
-      <c r="A23" s="200"/>
-      <c r="B23" s="221"/>
-      <c r="C23" s="186"/>
+      <c r="A23" s="199"/>
+      <c r="B23" s="220"/>
+      <c r="C23" s="185"/>
       <c r="D23" s="106"/>
-      <c r="E23" s="217"/>
-      <c r="F23" s="201"/>
-      <c r="G23" s="202"/>
-      <c r="H23" s="221"/>
-      <c r="I23" s="200"/>
+      <c r="E23" s="216"/>
+      <c r="F23" s="200"/>
+      <c r="G23" s="201"/>
+      <c r="H23" s="220"/>
+      <c r="I23" s="199"/>
     </row>
     <row r="24" spans="1:9" ht="13.7" customHeight="1">
-      <c r="A24" s="200"/>
-      <c r="B24" s="221"/>
+      <c r="A24" s="199"/>
+      <c r="B24" s="220"/>
       <c r="C24" s="8"/>
       <c r="D24" s="105"/>
-      <c r="E24" s="217"/>
-      <c r="F24" s="201"/>
-      <c r="G24" s="202"/>
-      <c r="H24" s="244"/>
-      <c r="I24" s="200"/>
+      <c r="E24" s="216"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="201"/>
+      <c r="H24" s="243"/>
+      <c r="I24" s="199"/>
     </row>
     <row r="25" spans="1:9" ht="13.7" customHeight="1">
-      <c r="A25" s="200"/>
-      <c r="B25" s="221"/>
+      <c r="A25" s="199"/>
+      <c r="B25" s="220"/>
       <c r="C25" s="8"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="217"/>
-      <c r="F25" s="201"/>
-      <c r="G25" s="202"/>
-      <c r="H25" s="180"/>
-      <c r="I25" s="200"/>
+      <c r="E25" s="216"/>
+      <c r="F25" s="200"/>
+      <c r="G25" s="201"/>
+      <c r="H25" s="179"/>
+      <c r="I25" s="199"/>
     </row>
     <row r="26" spans="1:9" ht="13.7" customHeight="1">
-      <c r="A26" s="200"/>
-      <c r="B26" s="221"/>
+      <c r="A26" s="199"/>
+      <c r="B26" s="220"/>
       <c r="C26" s="8"/>
       <c r="D26" s="104"/>
-      <c r="E26" s="217"/>
-      <c r="F26" s="201"/>
-      <c r="G26" s="202"/>
-      <c r="H26" s="180"/>
-      <c r="I26" s="200"/>
+      <c r="E26" s="216"/>
+      <c r="F26" s="200"/>
+      <c r="G26" s="201"/>
+      <c r="H26" s="179"/>
+      <c r="I26" s="199"/>
     </row>
     <row r="27" spans="1:9" ht="13.7" customHeight="1">
-      <c r="A27" s="200"/>
-      <c r="B27" s="221"/>
-      <c r="C27" s="219"/>
-      <c r="D27" s="229"/>
-      <c r="E27" s="217"/>
-      <c r="F27" s="201"/>
-      <c r="G27" s="202"/>
-      <c r="H27" s="180"/>
-      <c r="I27" s="200"/>
+      <c r="A27" s="199"/>
+      <c r="B27" s="220"/>
+      <c r="C27" s="218"/>
+      <c r="D27" s="228"/>
+      <c r="E27" s="216"/>
+      <c r="F27" s="200"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="179"/>
+      <c r="I27" s="199"/>
     </row>
     <row r="28" spans="1:9" ht="13.7" customHeight="1">
-      <c r="A28" s="200"/>
-      <c r="B28" s="221"/>
-      <c r="C28" s="219"/>
-      <c r="D28" s="229"/>
-      <c r="E28" s="217"/>
-      <c r="F28" s="201"/>
-      <c r="G28" s="202"/>
-      <c r="H28" s="180"/>
-      <c r="I28" s="200"/>
+      <c r="A28" s="199"/>
+      <c r="B28" s="220"/>
+      <c r="C28" s="218"/>
+      <c r="D28" s="228"/>
+      <c r="E28" s="216"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="201"/>
+      <c r="H28" s="179"/>
+      <c r="I28" s="199"/>
     </row>
     <row r="29" spans="1:9" ht="13.7" customHeight="1">
       <c r="A29" s="52"/>
-      <c r="B29" s="221"/>
+      <c r="B29" s="220"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="217"/>
-      <c r="F29" s="126"/>
-      <c r="G29" s="124"/>
-      <c r="H29" s="180"/>
+      <c r="D29" s="228"/>
+      <c r="E29" s="216"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="123"/>
+      <c r="H29" s="179"/>
       <c r="I29" s="52"/>
     </row>
     <row r="30" spans="1:9" ht="13.7" customHeight="1">
       <c r="A30" s="52"/>
-      <c r="B30" s="221"/>
-      <c r="C30" s="219"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="217"/>
-      <c r="F30" s="126"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="180"/>
+      <c r="B30" s="220"/>
+      <c r="C30" s="218"/>
+      <c r="D30" s="228"/>
+      <c r="E30" s="216"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="179"/>
       <c r="I30" s="52"/>
     </row>
     <row r="31" spans="1:9" ht="13.7" customHeight="1">
       <c r="A31" s="52"/>
-      <c r="B31" s="221"/>
+      <c r="B31" s="220"/>
       <c r="C31" s="8"/>
       <c r="D31" s="105"/>
-      <c r="E31" s="217"/>
-      <c r="F31" s="126"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="180"/>
+      <c r="E31" s="216"/>
+      <c r="F31" s="125"/>
+      <c r="G31" s="123"/>
+      <c r="H31" s="179"/>
       <c r="I31" s="52"/>
     </row>
     <row r="32" spans="1:9" ht="13.7" customHeight="1">
       <c r="A32" s="52"/>
-      <c r="B32" s="221"/>
-      <c r="C32" s="383"/>
-      <c r="D32" s="384"/>
-      <c r="E32" s="217"/>
-      <c r="F32" s="126"/>
-      <c r="G32" s="124"/>
-      <c r="H32" s="180"/>
+      <c r="B32" s="220"/>
+      <c r="C32" s="389"/>
+      <c r="D32" s="390"/>
+      <c r="E32" s="216"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="123"/>
+      <c r="H32" s="179"/>
       <c r="I32" s="52"/>
     </row>
     <row r="33" spans="1:15" ht="13.7" customHeight="1">
       <c r="A33" s="52"/>
-      <c r="B33" s="221"/>
-      <c r="C33" s="219"/>
-      <c r="D33" s="242"/>
-      <c r="E33" s="217"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="228"/>
+      <c r="B33" s="220"/>
+      <c r="C33" s="218"/>
+      <c r="D33" s="241"/>
+      <c r="E33" s="216"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="123"/>
+      <c r="H33" s="227"/>
       <c r="I33" s="52"/>
     </row>
     <row r="34" spans="1:15" ht="13.7" customHeight="1">
       <c r="A34" s="52"/>
-      <c r="B34" s="221"/>
-      <c r="C34" s="219"/>
-      <c r="D34" s="242"/>
-      <c r="E34" s="217"/>
-      <c r="F34" s="128"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="180"/>
+      <c r="B34" s="220"/>
+      <c r="C34" s="218"/>
+      <c r="D34" s="241"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="123"/>
+      <c r="H34" s="179"/>
       <c r="I34" s="52"/>
     </row>
     <row r="35" spans="1:15" ht="13.7" customHeight="1">
       <c r="A35" s="52"/>
-      <c r="B35" s="221"/>
-      <c r="C35" s="219"/>
-      <c r="D35" s="242"/>
-      <c r="E35" s="217"/>
-      <c r="F35" s="128"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="180"/>
+      <c r="B35" s="220"/>
+      <c r="C35" s="218"/>
+      <c r="D35" s="241"/>
+      <c r="E35" s="216"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="123"/>
+      <c r="H35" s="179"/>
       <c r="I35" s="52"/>
     </row>
     <row r="36" spans="1:15" ht="13.7" customHeight="1">
       <c r="A36" s="52"/>
-      <c r="B36" s="221"/>
-      <c r="C36" s="385"/>
-      <c r="D36" s="386"/>
-      <c r="E36" s="217"/>
-      <c r="F36" s="128"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="228"/>
+      <c r="B36" s="220"/>
+      <c r="C36" s="391"/>
+      <c r="D36" s="392"/>
+      <c r="E36" s="216"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="123"/>
+      <c r="H36" s="227"/>
       <c r="I36" s="52"/>
     </row>
     <row r="37" spans="1:15" ht="13.7" customHeight="1">
       <c r="A37" s="52"/>
-      <c r="B37" s="179"/>
-      <c r="C37" s="268"/>
-      <c r="D37" s="269"/>
-      <c r="E37" s="217"/>
-      <c r="F37" s="128"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="228"/>
+      <c r="B37" s="178"/>
+      <c r="C37" s="267"/>
+      <c r="D37" s="268"/>
+      <c r="E37" s="216"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="123"/>
+      <c r="H37" s="227"/>
       <c r="I37" s="52"/>
     </row>
     <row r="38" spans="1:15" ht="13.7" customHeight="1">
       <c r="A38" s="52"/>
-      <c r="B38" s="221"/>
+      <c r="B38" s="220"/>
       <c r="C38" s="8"/>
       <c r="D38" s="105"/>
-      <c r="E38" s="213"/>
-      <c r="F38" s="128"/>
-      <c r="G38" s="124"/>
-      <c r="H38" s="228"/>
+      <c r="E38" s="212"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="123"/>
+      <c r="H38" s="227"/>
       <c r="I38" s="52"/>
       <c r="M38" t="s">
         <v>84</v>
@@ -4222,57 +4216,57 @@
     </row>
     <row r="39" spans="1:15" ht="13.7" customHeight="1">
       <c r="A39" s="52"/>
-      <c r="B39" s="221"/>
-      <c r="C39" s="137"/>
-      <c r="D39" s="162"/>
+      <c r="B39" s="220"/>
+      <c r="C39" s="136"/>
+      <c r="D39" s="161"/>
       <c r="E39" s="54"/>
-      <c r="F39" s="128"/>
-      <c r="G39" s="124"/>
-      <c r="H39" s="228"/>
+      <c r="F39" s="127"/>
+      <c r="G39" s="123"/>
+      <c r="H39" s="227"/>
       <c r="I39" s="52"/>
     </row>
     <row r="40" spans="1:15" ht="13.7" customHeight="1">
       <c r="A40" s="52"/>
-      <c r="B40" s="221"/>
+      <c r="B40" s="220"/>
       <c r="C40" s="8"/>
       <c r="D40" s="104"/>
       <c r="E40" s="54"/>
-      <c r="F40" s="128"/>
-      <c r="G40" s="124"/>
-      <c r="H40" s="228"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="123"/>
+      <c r="H40" s="227"/>
       <c r="I40" s="52"/>
     </row>
     <row r="41" spans="1:15" ht="13.7" customHeight="1">
       <c r="A41" s="52"/>
-      <c r="B41" s="221"/>
-      <c r="C41" s="186"/>
-      <c r="D41" s="187"/>
+      <c r="B41" s="220"/>
+      <c r="C41" s="185"/>
+      <c r="D41" s="186"/>
       <c r="E41" s="54"/>
-      <c r="F41" s="128"/>
-      <c r="G41" s="124"/>
-      <c r="H41" s="228"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="123"/>
+      <c r="H41" s="227"/>
       <c r="I41" s="52"/>
     </row>
     <row r="42" spans="1:15" ht="13.7" customHeight="1">
       <c r="A42" s="52"/>
-      <c r="B42" s="221"/>
+      <c r="B42" s="220"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="162"/>
+      <c r="D42" s="161"/>
       <c r="E42" s="54"/>
-      <c r="F42" s="128"/>
-      <c r="G42" s="124"/>
-      <c r="H42" s="228"/>
+      <c r="F42" s="127"/>
+      <c r="G42" s="123"/>
+      <c r="H42" s="227"/>
       <c r="I42" s="52"/>
     </row>
     <row r="43" spans="1:15" ht="13.7" customHeight="1">
       <c r="A43" s="52"/>
-      <c r="B43" s="221"/>
-      <c r="C43" s="225"/>
+      <c r="B43" s="220"/>
+      <c r="C43" s="224"/>
       <c r="D43" s="105"/>
       <c r="E43" s="54"/>
-      <c r="F43" s="128"/>
-      <c r="G43" s="124"/>
-      <c r="H43" s="228"/>
+      <c r="F43" s="127"/>
+      <c r="G43" s="123"/>
+      <c r="H43" s="227"/>
       <c r="I43" s="52"/>
       <c r="O43" t="s">
         <v>84</v>
@@ -4280,234 +4274,234 @@
     </row>
     <row r="44" spans="1:15" ht="13.7" customHeight="1">
       <c r="A44" s="52"/>
-      <c r="B44" s="221"/>
+      <c r="B44" s="220"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="129"/>
+      <c r="D44" s="128"/>
       <c r="E44" s="54"/>
-      <c r="F44" s="128"/>
-      <c r="G44" s="124"/>
-      <c r="H44" s="228"/>
+      <c r="F44" s="127"/>
+      <c r="G44" s="123"/>
+      <c r="H44" s="227"/>
       <c r="I44" s="52"/>
     </row>
     <row r="45" spans="1:15" ht="13.7" customHeight="1">
       <c r="A45" s="52"/>
-      <c r="B45" s="221"/>
-      <c r="C45" s="387"/>
-      <c r="D45" s="388"/>
+      <c r="B45" s="220"/>
+      <c r="C45" s="393"/>
+      <c r="D45" s="394"/>
       <c r="E45" s="54"/>
-      <c r="F45" s="128"/>
-      <c r="G45" s="124"/>
-      <c r="H45" s="228"/>
+      <c r="F45" s="127"/>
+      <c r="G45" s="123"/>
+      <c r="H45" s="227"/>
       <c r="I45" s="52"/>
     </row>
     <row r="46" spans="1:15" ht="13.7" customHeight="1">
       <c r="A46" s="52"/>
-      <c r="B46" s="221"/>
+      <c r="B46" s="220"/>
       <c r="C46" s="12"/>
       <c r="D46" s="53"/>
-      <c r="E46" s="126"/>
-      <c r="F46" s="128"/>
-      <c r="G46" s="124"/>
-      <c r="H46" s="228"/>
+      <c r="E46" s="125"/>
+      <c r="F46" s="127"/>
+      <c r="G46" s="123"/>
+      <c r="H46" s="227"/>
       <c r="I46" s="52"/>
     </row>
     <row r="47" spans="1:15" ht="13.7" customHeight="1">
       <c r="A47" s="52"/>
-      <c r="B47" s="221"/>
+      <c r="B47" s="220"/>
       <c r="C47" s="12"/>
-      <c r="D47" s="129"/>
+      <c r="D47" s="128"/>
       <c r="E47" s="54"/>
-      <c r="F47" s="128"/>
-      <c r="G47" s="124"/>
-      <c r="H47" s="228"/>
+      <c r="F47" s="127"/>
+      <c r="G47" s="123"/>
+      <c r="H47" s="227"/>
       <c r="I47" s="52"/>
     </row>
     <row r="48" spans="1:15" ht="13.7" customHeight="1">
       <c r="A48" s="52"/>
-      <c r="B48" s="221"/>
+      <c r="B48" s="220"/>
       <c r="C48" s="12"/>
-      <c r="D48" s="129"/>
+      <c r="D48" s="128"/>
       <c r="E48" s="54"/>
-      <c r="F48" s="128"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="228"/>
+      <c r="F48" s="127"/>
+      <c r="G48" s="123"/>
+      <c r="H48" s="227"/>
       <c r="I48" s="52"/>
     </row>
     <row r="49" spans="1:13" ht="13.7" customHeight="1">
       <c r="A49" s="52"/>
-      <c r="B49" s="131"/>
-      <c r="C49" s="135"/>
-      <c r="D49" s="129"/>
+      <c r="B49" s="130"/>
+      <c r="C49" s="134"/>
+      <c r="D49" s="128"/>
       <c r="E49" s="54"/>
-      <c r="F49" s="128"/>
-      <c r="G49" s="124"/>
-      <c r="H49" s="228"/>
+      <c r="F49" s="127"/>
+      <c r="G49" s="123"/>
+      <c r="H49" s="227"/>
       <c r="I49" s="52"/>
     </row>
     <row r="50" spans="1:13" ht="13.7" hidden="1" customHeight="1">
       <c r="A50" s="52"/>
-      <c r="B50" s="221"/>
+      <c r="B50" s="220"/>
       <c r="C50" s="12"/>
       <c r="D50" s="46"/>
       <c r="E50" s="54"/>
-      <c r="F50" s="128"/>
-      <c r="G50" s="124"/>
-      <c r="H50" s="228"/>
+      <c r="F50" s="127"/>
+      <c r="G50" s="123"/>
+      <c r="H50" s="227"/>
       <c r="I50" s="52"/>
     </row>
     <row r="51" spans="1:13" ht="13.7" customHeight="1">
       <c r="A51" s="52"/>
-      <c r="B51" s="221"/>
-      <c r="C51" s="198"/>
-      <c r="D51" s="264"/>
+      <c r="B51" s="220"/>
+      <c r="C51" s="197"/>
+      <c r="D51" s="263"/>
       <c r="E51" s="54"/>
-      <c r="F51" s="128"/>
-      <c r="G51" s="124"/>
-      <c r="H51" s="176"/>
+      <c r="F51" s="127"/>
+      <c r="G51" s="123"/>
+      <c r="H51" s="175"/>
       <c r="I51" s="52"/>
     </row>
     <row r="52" spans="1:13" ht="13.7" customHeight="1">
       <c r="A52" s="52"/>
-      <c r="B52" s="131"/>
-      <c r="C52" s="267"/>
-      <c r="D52" s="265"/>
+      <c r="B52" s="130"/>
+      <c r="C52" s="266"/>
+      <c r="D52" s="264"/>
       <c r="E52" s="54"/>
-      <c r="F52" s="128"/>
-      <c r="G52" s="124"/>
-      <c r="H52" s="176"/>
+      <c r="F52" s="127"/>
+      <c r="G52" s="123"/>
+      <c r="H52" s="175"/>
       <c r="I52" s="52"/>
     </row>
     <row r="53" spans="1:13" ht="13.7" customHeight="1">
       <c r="A53" s="52"/>
-      <c r="B53" s="221"/>
+      <c r="B53" s="220"/>
       <c r="C53" s="71"/>
-      <c r="D53" s="246"/>
+      <c r="D53" s="245"/>
       <c r="E53" s="54"/>
-      <c r="F53" s="128"/>
-      <c r="G53" s="124"/>
-      <c r="H53" s="176"/>
+      <c r="F53" s="127"/>
+      <c r="G53" s="123"/>
+      <c r="H53" s="175"/>
       <c r="I53" s="52"/>
     </row>
     <row r="54" spans="1:13" ht="13.7" customHeight="1">
       <c r="A54" s="52"/>
-      <c r="B54" s="131"/>
-      <c r="C54" s="387"/>
-      <c r="D54" s="388"/>
+      <c r="B54" s="130"/>
+      <c r="C54" s="393"/>
+      <c r="D54" s="394"/>
       <c r="E54" s="54"/>
-      <c r="F54" s="128"/>
-      <c r="G54" s="124"/>
-      <c r="H54" s="176"/>
+      <c r="F54" s="127"/>
+      <c r="G54" s="123"/>
+      <c r="H54" s="175"/>
       <c r="I54" s="52"/>
     </row>
     <row r="55" spans="1:13" ht="13.7" customHeight="1">
-      <c r="A55" s="125" t="s">
+      <c r="A55" s="124" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="410" t="s">
+      <c r="B55" s="384" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="410"/>
-      <c r="D55" s="410"/>
-      <c r="E55" s="410"/>
-      <c r="F55" s="410"/>
-      <c r="G55" s="410"/>
-      <c r="H55" s="410"/>
-      <c r="I55" s="411"/>
+      <c r="C55" s="384"/>
+      <c r="D55" s="384"/>
+      <c r="E55" s="384"/>
+      <c r="F55" s="384"/>
+      <c r="G55" s="384"/>
+      <c r="H55" s="384"/>
+      <c r="I55" s="385"/>
     </row>
     <row r="56" spans="1:13" ht="13.7" customHeight="1">
       <c r="A56" s="19"/>
-      <c r="B56" s="412"/>
-      <c r="C56" s="412"/>
-      <c r="D56" s="412"/>
-      <c r="E56" s="412"/>
-      <c r="F56" s="412"/>
-      <c r="G56" s="412"/>
-      <c r="H56" s="412"/>
-      <c r="I56" s="413"/>
+      <c r="B56" s="386"/>
+      <c r="C56" s="386"/>
+      <c r="D56" s="386"/>
+      <c r="E56" s="386"/>
+      <c r="F56" s="386"/>
+      <c r="G56" s="386"/>
+      <c r="H56" s="386"/>
+      <c r="I56" s="387"/>
     </row>
     <row r="57" spans="1:13" ht="13.7" customHeight="1">
-      <c r="A57" s="325"/>
-      <c r="B57" s="326"/>
+      <c r="A57" s="368"/>
+      <c r="B57" s="369"/>
       <c r="C57" s="7" t="s">
         <v>48</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E57" s="325" t="s">
+      <c r="E57" s="368" t="s">
         <v>33</v>
       </c>
-      <c r="F57" s="414"/>
-      <c r="G57" s="326"/>
-      <c r="H57" s="325" t="s">
+      <c r="F57" s="388"/>
+      <c r="G57" s="369"/>
+      <c r="H57" s="368" t="s">
         <v>21</v>
       </c>
-      <c r="I57" s="326"/>
+      <c r="I57" s="369"/>
     </row>
     <row r="58" spans="1:13" ht="13.7" customHeight="1">
-      <c r="A58" s="325" t="s">
+      <c r="A58" s="368" t="s">
         <v>50</v>
       </c>
-      <c r="B58" s="326"/>
-      <c r="C58" s="233"/>
-      <c r="D58" s="233"/>
-      <c r="E58" s="398"/>
-      <c r="F58" s="399"/>
-      <c r="G58" s="400"/>
-      <c r="H58" s="398"/>
-      <c r="I58" s="400"/>
+      <c r="B58" s="369"/>
+      <c r="C58" s="232"/>
+      <c r="D58" s="232"/>
+      <c r="E58" s="372"/>
+      <c r="F58" s="373"/>
+      <c r="G58" s="374"/>
+      <c r="H58" s="372"/>
+      <c r="I58" s="374"/>
     </row>
     <row r="59" spans="1:13" ht="13.7" customHeight="1">
-      <c r="A59" s="396" t="s">
+      <c r="A59" s="377" t="s">
         <v>51</v>
       </c>
-      <c r="B59" s="397"/>
+      <c r="B59" s="378"/>
       <c r="C59" s="111" t="s">
         <v>94</v>
       </c>
       <c r="D59" s="111" t="s">
         <v>125</v>
       </c>
-      <c r="E59" s="405" t="s">
+      <c r="E59" s="379" t="s">
         <v>52</v>
       </c>
-      <c r="F59" s="406"/>
-      <c r="G59" s="407"/>
-      <c r="H59" s="408" t="s">
+      <c r="F59" s="380"/>
+      <c r="G59" s="381"/>
+      <c r="H59" s="382" t="s">
         <v>94</v>
       </c>
-      <c r="I59" s="409"/>
+      <c r="I59" s="383"/>
     </row>
     <row r="60" spans="1:13" ht="13.7" customHeight="1">
-      <c r="A60" s="325" t="s">
+      <c r="A60" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="B60" s="326"/>
-      <c r="C60" s="234"/>
-      <c r="D60" s="290" t="s">
+      <c r="B60" s="369"/>
+      <c r="C60" s="233"/>
+      <c r="D60" s="289" t="s">
         <v>83</v>
       </c>
-      <c r="E60" s="398" t="s">
+      <c r="E60" s="372" t="s">
         <v>54</v>
       </c>
-      <c r="F60" s="399"/>
-      <c r="G60" s="400"/>
-      <c r="H60" s="401">
+      <c r="F60" s="373"/>
+      <c r="G60" s="374"/>
+      <c r="H60" s="375">
         <v>46162</v>
       </c>
-      <c r="I60" s="402"/>
+      <c r="I60" s="376"/>
       <c r="M60" s="94"/>
     </row>
     <row r="61" spans="1:13" ht="13.7" customHeight="1">
-      <c r="A61" s="351"/>
-      <c r="B61" s="351"/>
-      <c r="C61" s="351"/>
-      <c r="D61" s="351"/>
-      <c r="E61" s="351"/>
-      <c r="F61" s="351"/>
-      <c r="G61" s="351"/>
-      <c r="H61" s="351"/>
-      <c r="I61" s="351"/>
+      <c r="A61" s="402"/>
+      <c r="B61" s="402"/>
+      <c r="C61" s="402"/>
+      <c r="D61" s="402"/>
+      <c r="E61" s="402"/>
+      <c r="F61" s="402"/>
+      <c r="G61" s="402"/>
+      <c r="H61" s="402"/>
+      <c r="I61" s="402"/>
     </row>
     <row r="62" spans="1:13" ht="13.7" customHeight="1">
       <c r="M62" s="49"/>
@@ -4935,6 +4929,31 @@
     <row r="17578" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="E60:G60"/>
     <mergeCell ref="H60:I60"/>
@@ -4951,31 +4970,6 @@
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="H57:I57"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A61:I61"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4997,249 +4991,249 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="421"/>
-      <c r="B1" s="422"/>
-      <c r="C1" s="422"/>
-      <c r="D1" s="422"/>
-      <c r="E1" s="423"/>
-      <c r="F1" s="355"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="357"/>
+      <c r="A1" s="329"/>
+      <c r="B1" s="330"/>
+      <c r="C1" s="330"/>
+      <c r="D1" s="330"/>
+      <c r="E1" s="331"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="333"/>
+      <c r="H1" s="334"/>
     </row>
     <row r="2" spans="1:8" ht="21">
-      <c r="A2" s="424" t="s">
+      <c r="A2" s="335" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="425"/>
-      <c r="C2" s="425"/>
-      <c r="D2" s="425"/>
-      <c r="E2" s="426"/>
-      <c r="F2" s="427" t="s">
+      <c r="B2" s="336"/>
+      <c r="C2" s="336"/>
+      <c r="D2" s="336"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="338" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="428"/>
-      <c r="H2" s="429"/>
+      <c r="G2" s="339"/>
+      <c r="H2" s="340"/>
     </row>
     <row r="3" spans="1:8" ht="21">
-      <c r="A3" s="424" t="s">
+      <c r="A3" s="335" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="425"/>
-      <c r="C3" s="425"/>
-      <c r="D3" s="425"/>
-      <c r="E3" s="426"/>
-      <c r="F3" s="427" t="s">
+      <c r="B3" s="336"/>
+      <c r="C3" s="336"/>
+      <c r="D3" s="336"/>
+      <c r="E3" s="337"/>
+      <c r="F3" s="338" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="428"/>
-      <c r="H3" s="429"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="340"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="370" t="s">
+      <c r="A4" s="341" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="371"/>
-      <c r="C4" s="371"/>
-      <c r="D4" s="371"/>
-      <c r="E4" s="372"/>
-      <c r="F4" s="370"/>
-      <c r="G4" s="371"/>
-      <c r="H4" s="372"/>
+      <c r="B4" s="342"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="343"/>
+      <c r="F4" s="341"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="343"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="370" t="s">
+      <c r="A5" s="341" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="371"/>
-      <c r="C5" s="371"/>
-      <c r="D5" s="371"/>
-      <c r="E5" s="372"/>
-      <c r="F5" s="370" t="s">
+      <c r="B5" s="342"/>
+      <c r="C5" s="342"/>
+      <c r="D5" s="342"/>
+      <c r="E5" s="343"/>
+      <c r="F5" s="341" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="371"/>
-      <c r="H5" s="372"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="343"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="376" t="s">
+      <c r="A6" s="344" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="377"/>
-      <c r="C6" s="377"/>
-      <c r="D6" s="377"/>
-      <c r="E6" s="378"/>
-      <c r="F6" s="376"/>
-      <c r="G6" s="377"/>
-      <c r="H6" s="378"/>
+      <c r="B6" s="345"/>
+      <c r="C6" s="345"/>
+      <c r="D6" s="345"/>
+      <c r="E6" s="346"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="345"/>
+      <c r="H6" s="346"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="430" t="s">
+      <c r="A7" s="305" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="431"/>
-      <c r="C7" s="121"/>
+      <c r="B7" s="306"/>
+      <c r="C7" s="120"/>
       <c r="D7" s="31"/>
       <c r="E7" s="10"/>
       <c r="F7" s="28"/>
       <c r="G7" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="120"/>
+      <c r="H7" s="119"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="432" t="s">
+      <c r="A8" s="347" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="433"/>
-      <c r="C8" s="284"/>
+      <c r="B8" s="348"/>
+      <c r="C8" s="283"/>
       <c r="D8" s="32"/>
       <c r="E8" s="10"/>
       <c r="F8" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="292"/>
-      <c r="H8" s="499"/>
+      <c r="G8" s="291"/>
+      <c r="H8" s="300"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
-      <c r="A9" s="436" t="s">
+      <c r="A9" s="316" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="436" t="s">
+      <c r="B9" s="316" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="438" t="s">
+      <c r="C9" s="318" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="382"/>
-      <c r="E9" s="439" t="s">
+      <c r="D9" s="319"/>
+      <c r="E9" s="320" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="440"/>
-      <c r="G9" s="443" t="s">
+      <c r="F9" s="321"/>
+      <c r="G9" s="324" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="434" t="s">
+      <c r="H9" s="309" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="437"/>
-      <c r="B10" s="437"/>
+      <c r="A10" s="317"/>
+      <c r="B10" s="317"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="441"/>
-      <c r="F10" s="442"/>
-      <c r="G10" s="444"/>
-      <c r="H10" s="435"/>
+      <c r="E10" s="322"/>
+      <c r="F10" s="323"/>
+      <c r="G10" s="325"/>
+      <c r="H10" s="310"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="81"/>
       <c r="B11" s="81"/>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
-      <c r="E11" s="268"/>
+      <c r="E11" s="267"/>
       <c r="F11" s="46"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="238"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="237"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="81"/>
       <c r="B12" s="81"/>
       <c r="C12" s="60"/>
       <c r="D12" s="60"/>
-      <c r="E12" s="297"/>
+      <c r="E12" s="296"/>
       <c r="F12" s="46"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="294"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="293"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="81"/>
       <c r="B13" s="81"/>
       <c r="C13" s="60"/>
       <c r="D13" s="60"/>
-      <c r="E13" s="268"/>
+      <c r="E13" s="267"/>
       <c r="F13" s="105"/>
       <c r="G13" s="64"/>
-      <c r="H13" s="294"/>
+      <c r="H13" s="293"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="81"/>
       <c r="B14" s="81"/>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
-      <c r="E14" s="275"/>
+      <c r="E14" s="274"/>
       <c r="F14" s="86"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="294"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="293"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="81"/>
       <c r="B15" s="81"/>
       <c r="C15" s="60"/>
       <c r="D15" s="60"/>
-      <c r="E15" s="403"/>
-      <c r="F15" s="404"/>
-      <c r="G15" s="140"/>
-      <c r="H15" s="294"/>
+      <c r="E15" s="311"/>
+      <c r="F15" s="312"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="293"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="82"/>
       <c r="B16" s="81"/>
       <c r="C16" s="60"/>
       <c r="D16" s="60"/>
-      <c r="E16" s="219"/>
+      <c r="E16" s="218"/>
       <c r="F16" s="46"/>
-      <c r="G16" s="299"/>
-      <c r="H16" s="294"/>
+      <c r="G16" s="298"/>
+      <c r="H16" s="293"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="82"/>
       <c r="B17" s="81"/>
       <c r="C17" s="60"/>
       <c r="D17" s="60"/>
-      <c r="E17" s="403"/>
-      <c r="F17" s="404"/>
+      <c r="E17" s="311"/>
+      <c r="F17" s="312"/>
       <c r="G17" s="64"/>
-      <c r="H17" s="294"/>
+      <c r="H17" s="293"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="81"/>
       <c r="B18" s="55"/>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
-      <c r="E18" s="219"/>
+      <c r="E18" s="218"/>
       <c r="F18" s="86"/>
       <c r="G18" s="64"/>
-      <c r="H18" s="294"/>
+      <c r="H18" s="293"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="295"/>
+      <c r="A19" s="294"/>
       <c r="B19" s="55"/>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
-      <c r="E19" s="219"/>
+      <c r="E19" s="218"/>
       <c r="F19" s="86"/>
       <c r="G19" s="64"/>
-      <c r="H19" s="294"/>
+      <c r="H19" s="293"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
-      <c r="A20" s="295"/>
+      <c r="A20" s="294"/>
       <c r="B20" s="81"/>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
-      <c r="E20" s="268"/>
+      <c r="E20" s="267"/>
       <c r="F20" s="86"/>
       <c r="G20" s="64"/>
       <c r="H20" s="51"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="295"/>
+      <c r="A21" s="294"/>
       <c r="B21" s="55"/>
       <c r="C21" s="61"/>
       <c r="D21" s="61"/>
-      <c r="E21" s="186"/>
+      <c r="E21" s="185"/>
       <c r="F21" s="47"/>
       <c r="G21" s="64"/>
       <c r="H21" s="51"/>
@@ -5249,10 +5243,10 @@
       <c r="B22" s="82"/>
       <c r="C22" s="61"/>
       <c r="D22" s="61"/>
-      <c r="E22" s="445"/>
-      <c r="F22" s="446"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="304"/>
       <c r="G22" s="64"/>
-      <c r="H22" s="233"/>
+      <c r="H22" s="232"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="82"/>
@@ -5262,7 +5256,7 @@
       <c r="E23" s="44"/>
       <c r="F23" s="86"/>
       <c r="G23" s="63"/>
-      <c r="H23" s="233"/>
+      <c r="H23" s="232"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="82"/>
@@ -5272,7 +5266,7 @@
       <c r="E24" s="50"/>
       <c r="F24" s="107"/>
       <c r="G24" s="63"/>
-      <c r="H24" s="233"/>
+      <c r="H24" s="232"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="81"/>
@@ -5282,7 +5276,7 @@
       <c r="E25" s="11"/>
       <c r="F25" s="86"/>
       <c r="G25" s="63"/>
-      <c r="H25" s="290"/>
+      <c r="H25" s="289"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="81"/>
@@ -5292,7 +5286,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="86"/>
       <c r="G26" s="63"/>
-      <c r="H26" s="290"/>
+      <c r="H26" s="289"/>
     </row>
     <row r="27" spans="1:8" ht="16.5" customHeight="1">
       <c r="A27" s="81"/>
@@ -5302,7 +5296,7 @@
       <c r="E27" s="44"/>
       <c r="F27" s="86"/>
       <c r="G27" s="103"/>
-      <c r="H27" s="290"/>
+      <c r="H27" s="289"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="81"/>
@@ -5312,7 +5306,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="85"/>
       <c r="G28" s="63"/>
-      <c r="H28" s="290"/>
+      <c r="H28" s="289"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="55"/>
@@ -5322,7 +5316,7 @@
       <c r="E29" s="44"/>
       <c r="F29" s="85"/>
       <c r="G29" s="63"/>
-      <c r="H29" s="290"/>
+      <c r="H29" s="289"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="55"/>
@@ -5332,7 +5326,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="76"/>
       <c r="G30" s="63"/>
-      <c r="H30" s="236"/>
+      <c r="H30" s="235"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="55"/>
@@ -5342,7 +5336,7 @@
       <c r="E31" s="44"/>
       <c r="F31" s="85"/>
       <c r="G31" s="63"/>
-      <c r="H31" s="236"/>
+      <c r="H31" s="235"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="55"/>
@@ -5352,7 +5346,7 @@
       <c r="E32" s="44"/>
       <c r="F32" s="85"/>
       <c r="G32" s="63"/>
-      <c r="H32" s="236"/>
+      <c r="H32" s="235"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="81"/>
@@ -5362,7 +5356,7 @@
       <c r="E33" s="84"/>
       <c r="F33" s="86"/>
       <c r="G33" s="63"/>
-      <c r="H33" s="236"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="81"/>
@@ -5372,7 +5366,7 @@
       <c r="E34" s="44"/>
       <c r="F34" s="85"/>
       <c r="G34" s="63"/>
-      <c r="H34" s="290"/>
+      <c r="H34" s="289"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="81"/>
@@ -5382,7 +5376,7 @@
       <c r="E35" s="44"/>
       <c r="F35" s="85"/>
       <c r="G35" s="63"/>
-      <c r="H35" s="290"/>
+      <c r="H35" s="289"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="82"/>
@@ -5392,7 +5386,7 @@
       <c r="E36" s="84"/>
       <c r="F36" s="86"/>
       <c r="G36" s="63"/>
-      <c r="H36" s="290"/>
+      <c r="H36" s="289"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="82"/>
@@ -5402,7 +5396,7 @@
       <c r="E37" s="99"/>
       <c r="F37" s="85"/>
       <c r="G37" s="63"/>
-      <c r="H37" s="290"/>
+      <c r="H37" s="289"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="82"/>
@@ -5412,7 +5406,7 @@
       <c r="E38" s="45"/>
       <c r="F38" s="85"/>
       <c r="G38" s="63"/>
-      <c r="H38" s="290"/>
+      <c r="H38" s="289"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="82"/>
@@ -5422,7 +5416,7 @@
       <c r="E39" s="45"/>
       <c r="F39" s="5"/>
       <c r="G39" s="63"/>
-      <c r="H39" s="290"/>
+      <c r="H39" s="289"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="82"/>
@@ -5432,7 +5426,7 @@
       <c r="E40" s="45"/>
       <c r="F40" s="85"/>
       <c r="G40" s="63"/>
-      <c r="H40" s="290"/>
+      <c r="H40" s="289"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="82"/>
@@ -5442,7 +5436,7 @@
       <c r="E41" s="11"/>
       <c r="F41" s="85"/>
       <c r="G41" s="63"/>
-      <c r="H41" s="290"/>
+      <c r="H41" s="289"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="82"/>
@@ -5452,7 +5446,7 @@
       <c r="E42" s="45"/>
       <c r="F42" s="5"/>
       <c r="G42" s="63"/>
-      <c r="H42" s="290"/>
+      <c r="H42" s="289"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="82"/>
@@ -5462,7 +5456,7 @@
       <c r="E43" s="45"/>
       <c r="F43" s="5"/>
       <c r="G43" s="63"/>
-      <c r="H43" s="290"/>
+      <c r="H43" s="289"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="82"/>
@@ -5472,7 +5466,7 @@
       <c r="E44" s="84"/>
       <c r="F44" s="85"/>
       <c r="G44" s="63"/>
-      <c r="H44" s="290"/>
+      <c r="H44" s="289"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="55"/>
@@ -5482,7 +5476,7 @@
       <c r="E45" s="45"/>
       <c r="F45" s="5"/>
       <c r="G45" s="63"/>
-      <c r="H45" s="290"/>
+      <c r="H45" s="289"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="72"/>
@@ -5492,7 +5486,7 @@
       <c r="E46" s="84"/>
       <c r="F46" s="85"/>
       <c r="G46" s="75"/>
-      <c r="H46" s="291"/>
+      <c r="H46" s="290"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="72"/>
@@ -5502,222 +5496,222 @@
       <c r="E47" s="71"/>
       <c r="F47" s="70"/>
       <c r="G47" s="75"/>
-      <c r="H47" s="291"/>
+      <c r="H47" s="290"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="430" t="s">
+      <c r="A48" s="305" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="431"/>
-      <c r="C48" s="431"/>
-      <c r="D48" s="431"/>
-      <c r="E48" s="293"/>
-      <c r="F48" s="430" t="s">
+      <c r="B48" s="306"/>
+      <c r="C48" s="306"/>
+      <c r="D48" s="306"/>
+      <c r="E48" s="292"/>
+      <c r="F48" s="305" t="s">
         <v>21</v>
       </c>
-      <c r="G48" s="431"/>
-      <c r="H48" s="447"/>
+      <c r="G48" s="306"/>
+      <c r="H48" s="307"/>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="330"/>
-      <c r="B49" s="331"/>
-      <c r="C49" s="331"/>
-      <c r="D49" s="331"/>
-      <c r="E49" s="331"/>
-      <c r="F49" s="330"/>
-      <c r="G49" s="331"/>
-      <c r="H49" s="332"/>
+      <c r="A49" s="301"/>
+      <c r="B49" s="302"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="301"/>
+      <c r="G49" s="302"/>
+      <c r="H49" s="308"/>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="327" t="s">
+      <c r="A50" s="313" t="s">
         <v>128</v>
       </c>
-      <c r="B50" s="328"/>
-      <c r="C50" s="328"/>
-      <c r="D50" s="328"/>
-      <c r="E50" s="328"/>
-      <c r="F50" s="327"/>
-      <c r="G50" s="328"/>
-      <c r="H50" s="329"/>
+      <c r="B50" s="314"/>
+      <c r="C50" s="314"/>
+      <c r="D50" s="314"/>
+      <c r="E50" s="314"/>
+      <c r="F50" s="313"/>
+      <c r="G50" s="314"/>
+      <c r="H50" s="315"/>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="330" t="s">
+      <c r="A51" s="301" t="s">
         <v>22</v>
       </c>
-      <c r="B51" s="331"/>
-      <c r="C51" s="331"/>
-      <c r="D51" s="331"/>
-      <c r="E51" s="331"/>
-      <c r="F51" s="330" t="s">
+      <c r="B51" s="302"/>
+      <c r="C51" s="302"/>
+      <c r="D51" s="302"/>
+      <c r="E51" s="302"/>
+      <c r="F51" s="301" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="331"/>
-      <c r="H51" s="332"/>
+      <c r="G51" s="302"/>
+      <c r="H51" s="308"/>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="415" t="s">
+      <c r="A52" s="349" t="s">
         <v>24</v>
       </c>
-      <c r="B52" s="416"/>
-      <c r="C52" s="416"/>
-      <c r="D52" s="416"/>
-      <c r="E52" s="416"/>
-      <c r="F52" s="327"/>
-      <c r="G52" s="328"/>
-      <c r="H52" s="329"/>
+      <c r="B52" s="350"/>
+      <c r="C52" s="350"/>
+      <c r="D52" s="350"/>
+      <c r="E52" s="350"/>
+      <c r="F52" s="313"/>
+      <c r="G52" s="314"/>
+      <c r="H52" s="315"/>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="333"/>
-      <c r="B53" s="417"/>
-      <c r="C53" s="417"/>
-      <c r="D53" s="417"/>
-      <c r="E53" s="417"/>
-      <c r="F53" s="330" t="s">
+      <c r="A53" s="351"/>
+      <c r="B53" s="352"/>
+      <c r="C53" s="352"/>
+      <c r="D53" s="352"/>
+      <c r="E53" s="352"/>
+      <c r="F53" s="301" t="s">
         <v>24</v>
       </c>
-      <c r="G53" s="331"/>
-      <c r="H53" s="332"/>
+      <c r="G53" s="302"/>
+      <c r="H53" s="308"/>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="330" t="s">
+      <c r="A54" s="301" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="331"/>
-      <c r="C54" s="331"/>
-      <c r="D54" s="331"/>
-      <c r="E54" s="331"/>
-      <c r="F54" s="418"/>
-      <c r="G54" s="419"/>
-      <c r="H54" s="420"/>
+      <c r="B54" s="302"/>
+      <c r="C54" s="302"/>
+      <c r="D54" s="302"/>
+      <c r="E54" s="302"/>
+      <c r="F54" s="353"/>
+      <c r="G54" s="354"/>
+      <c r="H54" s="355"/>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="338"/>
-      <c r="B55" s="339"/>
-      <c r="C55" s="339"/>
-      <c r="D55" s="339"/>
-      <c r="E55" s="339"/>
-      <c r="F55" s="338" t="s">
+      <c r="A55" s="326"/>
+      <c r="B55" s="327"/>
+      <c r="C55" s="327"/>
+      <c r="D55" s="327"/>
+      <c r="E55" s="327"/>
+      <c r="F55" s="326" t="s">
         <v>25</v>
       </c>
-      <c r="G55" s="339"/>
-      <c r="H55" s="340"/>
+      <c r="G55" s="327"/>
+      <c r="H55" s="328"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="N61" s="262"/>
+      <c r="N61" s="261"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="N62" s="262"/>
+      <c r="N62" s="261"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="N63" s="262"/>
+      <c r="N63" s="261"/>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
-      <c r="N64" s="262"/>
+      <c r="N64" s="261"/>
     </row>
     <row r="65" spans="14:14">
-      <c r="N65" s="262"/>
+      <c r="N65" s="261"/>
     </row>
     <row r="66" spans="14:14">
-      <c r="N66" s="262"/>
+      <c r="N66" s="261"/>
     </row>
     <row r="67" spans="14:14">
-      <c r="N67" s="262"/>
+      <c r="N67" s="261"/>
     </row>
     <row r="68" spans="14:14">
-      <c r="N68" s="262"/>
+      <c r="N68" s="261"/>
     </row>
     <row r="69" spans="14:14">
-      <c r="N69" s="262"/>
+      <c r="N69" s="261"/>
     </row>
     <row r="70" spans="14:14">
-      <c r="N70" s="263"/>
+      <c r="N70" s="262"/>
     </row>
     <row r="71" spans="14:14">
-      <c r="N71" s="262"/>
+      <c r="N71" s="261"/>
     </row>
     <row r="72" spans="14:14">
-      <c r="N72" s="262"/>
+      <c r="N72" s="261"/>
     </row>
     <row r="73" spans="14:14">
-      <c r="N73" s="262"/>
+      <c r="N73" s="261"/>
     </row>
     <row r="74" spans="14:14">
-      <c r="N74" s="262"/>
+      <c r="N74" s="261"/>
     </row>
     <row r="75" spans="14:14">
-      <c r="N75" s="262"/>
+      <c r="N75" s="261"/>
     </row>
     <row r="76" spans="14:14">
-      <c r="N76" s="262"/>
+      <c r="N76" s="261"/>
     </row>
     <row r="77" spans="14:14">
-      <c r="N77" s="262"/>
+      <c r="N77" s="261"/>
     </row>
     <row r="78" spans="14:14">
-      <c r="N78" s="262"/>
+      <c r="N78" s="261"/>
     </row>
     <row r="79" spans="14:14">
-      <c r="N79" s="262"/>
+      <c r="N79" s="261"/>
     </row>
     <row r="80" spans="14:14">
-      <c r="N80" s="262"/>
+      <c r="N80" s="261"/>
     </row>
     <row r="81" spans="14:14">
-      <c r="N81" s="262"/>
+      <c r="N81" s="261"/>
     </row>
     <row r="82" spans="14:14">
-      <c r="N82" s="262"/>
+      <c r="N82" s="261"/>
     </row>
     <row r="83" spans="14:14">
-      <c r="N83" s="262"/>
+      <c r="N83" s="261"/>
     </row>
     <row r="84" spans="14:14">
-      <c r="N84" s="262"/>
+      <c r="N84" s="261"/>
     </row>
     <row r="85" spans="14:14">
-      <c r="N85" s="262"/>
+      <c r="N85" s="261"/>
     </row>
     <row r="86" spans="14:14">
-      <c r="N86" s="262"/>
+      <c r="N86" s="261"/>
     </row>
     <row r="87" spans="14:14">
-      <c r="N87" s="262"/>
+      <c r="N87" s="261"/>
     </row>
     <row r="88" spans="14:14">
-      <c r="N88" s="262"/>
+      <c r="N88" s="261"/>
     </row>
     <row r="89" spans="14:14">
-      <c r="N89" s="262"/>
+      <c r="N89" s="261"/>
     </row>
     <row r="90" spans="14:14">
-      <c r="N90" s="262"/>
+      <c r="N90" s="261"/>
     </row>
     <row r="91" spans="14:14">
-      <c r="N91" s="262"/>
+      <c r="N91" s="261"/>
     </row>
     <row r="92" spans="14:14">
-      <c r="N92" s="262"/>
+      <c r="N92" s="261"/>
     </row>
     <row r="93" spans="14:14">
-      <c r="N93" s="262"/>
+      <c r="N93" s="261"/>
     </row>
     <row r="94" spans="14:14">
-      <c r="N94" s="262"/>
+      <c r="N94" s="261"/>
     </row>
     <row r="95" spans="14:14">
-      <c r="N95" s="262"/>
+      <c r="N95" s="261"/>
     </row>
     <row r="96" spans="14:14">
-      <c r="N96" s="262"/>
+      <c r="N96" s="261"/>
     </row>
     <row r="97" spans="14:14">
-      <c r="N97" s="262"/>
+      <c r="N97" s="261"/>
     </row>
     <row r="98" spans="14:14">
-      <c r="N98" s="262"/>
+      <c r="N98" s="261"/>
     </row>
     <row r="100" spans="14:14">
-      <c r="N100" s="261"/>
+      <c r="N100" s="260"/>
     </row>
     <row r="119" ht="15" customHeight="1"/>
     <row r="174" ht="15" customHeight="1"/>
@@ -5927,23 +5921,12 @@
     <row r="10723" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="F54:H54"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="A1:E1"/>
@@ -5960,12 +5943,23 @@
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F51:H51"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39300000000000002" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -5985,68 +5979,68 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
-      <c r="A2" s="443" t="s">
+      <c r="A2" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="443"/>
-      <c r="C2" s="443"/>
-      <c r="D2" s="449"/>
-      <c r="E2" s="449"/>
-      <c r="F2" s="449"/>
+      <c r="B2" s="324"/>
+      <c r="C2" s="324"/>
+      <c r="D2" s="427"/>
+      <c r="E2" s="427"/>
+      <c r="F2" s="427"/>
     </row>
     <row r="3" spans="1:8" ht="21">
-      <c r="A3" s="450" t="s">
+      <c r="A3" s="428" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="450"/>
-      <c r="C3" s="450"/>
-      <c r="D3" s="451" t="s">
+      <c r="B3" s="428"/>
+      <c r="C3" s="428"/>
+      <c r="D3" s="429" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="451"/>
-      <c r="F3" s="451"/>
+      <c r="E3" s="429"/>
+      <c r="F3" s="429"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
-      <c r="A4" s="452"/>
-      <c r="B4" s="452"/>
-      <c r="C4" s="452"/>
-      <c r="D4" s="453" t="s">
+      <c r="A4" s="430"/>
+      <c r="B4" s="430"/>
+      <c r="C4" s="430"/>
+      <c r="D4" s="431" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="454"/>
-      <c r="F4" s="455"/>
+      <c r="E4" s="432"/>
+      <c r="F4" s="433"/>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1">
-      <c r="A5" s="452" t="s">
+      <c r="A5" s="430" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="452"/>
-      <c r="C5" s="452"/>
-      <c r="D5" s="456"/>
-      <c r="E5" s="457"/>
-      <c r="F5" s="458"/>
+      <c r="B5" s="430"/>
+      <c r="C5" s="430"/>
+      <c r="D5" s="434"/>
+      <c r="E5" s="435"/>
+      <c r="F5" s="436"/>
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1">
-      <c r="A6" s="452" t="s">
+      <c r="A6" s="430" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="452"/>
-      <c r="C6" s="452"/>
-      <c r="D6" s="459" t="s">
+      <c r="B6" s="430"/>
+      <c r="C6" s="430"/>
+      <c r="D6" s="437" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="459"/>
-      <c r="F6" s="459"/>
+      <c r="E6" s="437"/>
+      <c r="F6" s="437"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
-      <c r="A7" s="460" t="s">
+      <c r="A7" s="438" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="460"/>
-      <c r="C7" s="460"/>
-      <c r="D7" s="461"/>
-      <c r="E7" s="461"/>
-      <c r="F7" s="461"/>
+      <c r="B7" s="438"/>
+      <c r="C7" s="438"/>
+      <c r="D7" s="439"/>
+      <c r="E7" s="439"/>
+      <c r="F7" s="439"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="21" t="s">
@@ -6062,20 +6056,20 @@
       <c r="A9" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="197"/>
+      <c r="B9" s="196"/>
       <c r="C9" s="3"/>
       <c r="D9" s="16"/>
       <c r="E9" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="288"/>
+      <c r="F9" s="287"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="289"/>
-      <c r="C10" s="132"/>
+      <c r="B10" s="288"/>
+      <c r="C10" s="131"/>
       <c r="D10" s="16"/>
       <c r="E10" s="10" t="s">
         <v>55</v>
@@ -6092,7 +6086,7 @@
       <c r="E11" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="212"/>
+      <c r="F11" s="211"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="25" t="s">
@@ -6107,267 +6101,267 @@
       <c r="F12" s="93"/>
     </row>
     <row r="13" spans="1:8" ht="30">
-      <c r="A13" s="236" t="s">
+      <c r="A13" s="235" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="392" t="s">
+      <c r="B13" s="398" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="392"/>
-      <c r="D13" s="392"/>
-      <c r="E13" s="235" t="s">
+      <c r="C13" s="398"/>
+      <c r="D13" s="398"/>
+      <c r="E13" s="234" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="235" t="s">
+      <c r="F13" s="234" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="7"/>
       <c r="B14" s="8"/>
-      <c r="C14" s="139"/>
+      <c r="C14" s="138"/>
       <c r="D14" s="76"/>
-      <c r="E14" s="221"/>
-      <c r="F14" s="221"/>
+      <c r="E14" s="220"/>
+      <c r="F14" s="220"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="7"/>
       <c r="B15" s="8"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="229"/>
-      <c r="E15" s="221"/>
-      <c r="F15" s="221"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="228"/>
+      <c r="E15" s="220"/>
+      <c r="F15" s="220"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="7"/>
-      <c r="B16" s="268"/>
-      <c r="C16" s="277"/>
-      <c r="D16" s="276"/>
-      <c r="E16" s="221"/>
-      <c r="F16" s="221"/>
-      <c r="H16" s="273"/>
+      <c r="B16" s="267"/>
+      <c r="C16" s="276"/>
+      <c r="D16" s="275"/>
+      <c r="E16" s="220"/>
+      <c r="F16" s="220"/>
+      <c r="H16" s="272"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="7"/>
-      <c r="B17" s="297"/>
-      <c r="C17" s="277"/>
-      <c r="D17" s="276"/>
-      <c r="E17" s="221"/>
-      <c r="F17" s="221"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="276"/>
+      <c r="D17" s="275"/>
+      <c r="E17" s="220"/>
+      <c r="F17" s="220"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1">
       <c r="A18" s="7"/>
-      <c r="B18" s="268"/>
-      <c r="C18" s="277"/>
-      <c r="D18" s="276"/>
-      <c r="E18" s="221"/>
-      <c r="F18" s="228"/>
+      <c r="B18" s="267"/>
+      <c r="C18" s="276"/>
+      <c r="D18" s="275"/>
+      <c r="E18" s="220"/>
+      <c r="F18" s="227"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1">
       <c r="A19" s="7"/>
-      <c r="B19" s="275"/>
-      <c r="C19" s="277"/>
-      <c r="D19" s="276"/>
-      <c r="E19" s="221"/>
-      <c r="F19" s="228"/>
+      <c r="B19" s="274"/>
+      <c r="C19" s="276"/>
+      <c r="D19" s="275"/>
+      <c r="E19" s="220"/>
+      <c r="F19" s="227"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="403"/>
-      <c r="C20" s="448"/>
-      <c r="D20" s="404"/>
-      <c r="E20" s="221"/>
-      <c r="F20" s="228"/>
-      <c r="I20" s="273"/>
+      <c r="B20" s="311"/>
+      <c r="C20" s="424"/>
+      <c r="D20" s="312"/>
+      <c r="E20" s="220"/>
+      <c r="F20" s="227"/>
+      <c r="I20" s="272"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1">
       <c r="A21" s="15"/>
-      <c r="B21" s="219"/>
-      <c r="C21" s="199"/>
-      <c r="D21" s="207"/>
-      <c r="E21" s="221"/>
-      <c r="F21" s="228"/>
-      <c r="K21" s="273"/>
+      <c r="B21" s="218"/>
+      <c r="C21" s="198"/>
+      <c r="D21" s="206"/>
+      <c r="E21" s="220"/>
+      <c r="F21" s="227"/>
+      <c r="K21" s="272"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1">
       <c r="A22" s="15"/>
-      <c r="B22" s="403"/>
-      <c r="C22" s="448"/>
-      <c r="D22" s="404"/>
-      <c r="E22" s="221"/>
-      <c r="F22" s="230"/>
+      <c r="B22" s="311"/>
+      <c r="C22" s="424"/>
+      <c r="D22" s="312"/>
+      <c r="E22" s="220"/>
+      <c r="F22" s="229"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1">
       <c r="A23" s="15"/>
-      <c r="B23" s="268"/>
-      <c r="C23" s="271"/>
+      <c r="B23" s="267"/>
+      <c r="C23" s="270"/>
       <c r="D23" s="105"/>
-      <c r="E23" s="221"/>
-      <c r="F23" s="221"/>
+      <c r="E23" s="220"/>
+      <c r="F23" s="220"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1">
       <c r="A24" s="7"/>
-      <c r="B24" s="186"/>
-      <c r="C24" s="270"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="269"/>
       <c r="D24" s="105"/>
-      <c r="E24" s="221"/>
-      <c r="F24" s="221"/>
+      <c r="E24" s="220"/>
+      <c r="F24" s="220"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1">
       <c r="A25" s="7"/>
-      <c r="B25" s="186"/>
-      <c r="C25" s="270"/>
+      <c r="B25" s="185"/>
+      <c r="C25" s="269"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="221"/>
-      <c r="F25" s="244"/>
+      <c r="E25" s="220"/>
+      <c r="F25" s="243"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="8"/>
-      <c r="C26" s="199"/>
-      <c r="D26" s="229"/>
-      <c r="E26" s="221"/>
-      <c r="F26" s="244"/>
+      <c r="C26" s="198"/>
+      <c r="D26" s="228"/>
+      <c r="E26" s="220"/>
+      <c r="F26" s="243"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="8"/>
-      <c r="C27" s="199"/>
+      <c r="C27" s="198"/>
       <c r="D27" s="105"/>
-      <c r="E27" s="221"/>
-      <c r="F27" s="180"/>
+      <c r="E27" s="220"/>
+      <c r="F27" s="179"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="8"/>
-      <c r="C28" s="139"/>
-      <c r="D28" s="229"/>
-      <c r="E28" s="221"/>
-      <c r="F28" s="180"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="228"/>
+      <c r="E28" s="220"/>
+      <c r="F28" s="179"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1">
       <c r="A29" s="7"/>
-      <c r="B29" s="219"/>
-      <c r="C29" s="241"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="221"/>
-      <c r="F29" s="180"/>
+      <c r="B29" s="218"/>
+      <c r="C29" s="240"/>
+      <c r="D29" s="228"/>
+      <c r="E29" s="220"/>
+      <c r="F29" s="179"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1">
       <c r="A30" s="7"/>
-      <c r="B30" s="219"/>
-      <c r="C30" s="241"/>
+      <c r="B30" s="218"/>
+      <c r="C30" s="240"/>
       <c r="D30" s="105"/>
-      <c r="E30" s="221"/>
-      <c r="F30" s="180"/>
+      <c r="E30" s="220"/>
+      <c r="F30" s="179"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="8"/>
-      <c r="C31" s="241"/>
+      <c r="C31" s="240"/>
       <c r="D31" s="105"/>
-      <c r="E31" s="221"/>
-      <c r="F31" s="180"/>
+      <c r="E31" s="220"/>
+      <c r="F31" s="179"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1">
       <c r="A32" s="7"/>
-      <c r="B32" s="219"/>
-      <c r="C32" s="241"/>
-      <c r="D32" s="211"/>
-      <c r="E32" s="221"/>
-      <c r="F32" s="180"/>
+      <c r="B32" s="218"/>
+      <c r="C32" s="240"/>
+      <c r="D32" s="210"/>
+      <c r="E32" s="220"/>
+      <c r="F32" s="179"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1">
       <c r="A33" s="7"/>
       <c r="B33" s="8"/>
-      <c r="C33" s="199"/>
+      <c r="C33" s="198"/>
       <c r="D33" s="105"/>
-      <c r="E33" s="221"/>
-      <c r="F33" s="180"/>
+      <c r="E33" s="220"/>
+      <c r="F33" s="179"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1">
       <c r="A34" s="7"/>
-      <c r="B34" s="403"/>
-      <c r="C34" s="448"/>
-      <c r="D34" s="404"/>
-      <c r="E34" s="221"/>
-      <c r="F34" s="151"/>
+      <c r="B34" s="311"/>
+      <c r="C34" s="424"/>
+      <c r="D34" s="312"/>
+      <c r="E34" s="220"/>
+      <c r="F34" s="150"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1">
       <c r="A35" s="7"/>
-      <c r="B35" s="248"/>
-      <c r="C35" s="249"/>
+      <c r="B35" s="247"/>
+      <c r="C35" s="248"/>
       <c r="D35" s="106"/>
-      <c r="E35" s="221"/>
-      <c r="F35" s="176"/>
+      <c r="E35" s="220"/>
+      <c r="F35" s="175"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1">
       <c r="A36" s="7"/>
-      <c r="B36" s="250"/>
-      <c r="C36" s="251"/>
+      <c r="B36" s="249"/>
+      <c r="C36" s="250"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="179"/>
-      <c r="F36" s="176"/>
+      <c r="E36" s="178"/>
+      <c r="F36" s="175"/>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1">
       <c r="A37" s="7"/>
-      <c r="B37" s="225"/>
-      <c r="C37" s="199"/>
+      <c r="B37" s="224"/>
+      <c r="C37" s="198"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="221"/>
-      <c r="F37" s="176"/>
+      <c r="E37" s="220"/>
+      <c r="F37" s="175"/>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1">
       <c r="A38" s="7"/>
-      <c r="B38" s="137"/>
+      <c r="B38" s="136"/>
       <c r="C38" s="110"/>
       <c r="D38" s="76"/>
-      <c r="E38" s="221"/>
-      <c r="F38" s="228"/>
+      <c r="E38" s="220"/>
+      <c r="F38" s="227"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1">
       <c r="A39" s="7"/>
       <c r="B39" s="8"/>
-      <c r="C39" s="119"/>
+      <c r="C39" s="118"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="221"/>
-      <c r="F39" s="228"/>
+      <c r="E39" s="220"/>
+      <c r="F39" s="227"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="71"/>
-      <c r="C40" s="119"/>
+      <c r="C40" s="118"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="221"/>
-      <c r="F40" s="228"/>
+      <c r="E40" s="220"/>
+      <c r="F40" s="227"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" s="7"/>
-      <c r="B41" s="445"/>
-      <c r="C41" s="462"/>
-      <c r="D41" s="446"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="130"/>
+      <c r="B41" s="303"/>
+      <c r="C41" s="425"/>
+      <c r="D41" s="304"/>
+      <c r="E41" s="130"/>
+      <c r="F41" s="129"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1">
       <c r="A42" s="7"/>
       <c r="B42" s="57"/>
-      <c r="C42" s="119"/>
+      <c r="C42" s="118"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="131"/>
-      <c r="F42" s="130"/>
+      <c r="E42" s="130"/>
+      <c r="F42" s="129"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1">
-      <c r="A43" s="463" t="s">
+      <c r="A43" s="426" t="s">
         <v>63</v>
       </c>
-      <c r="B43" s="463"/>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463" t="s">
+      <c r="B43" s="426"/>
+      <c r="C43" s="426"/>
+      <c r="D43" s="426" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="E43" s="426"/>
+      <c r="F43" s="426"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1">
       <c r="A44" s="42"/>
@@ -6381,13 +6375,13 @@
       <c r="A45" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="132"/>
+      <c r="B45" s="131"/>
       <c r="C45" s="26"/>
       <c r="D45" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="132"/>
-      <c r="F45" s="220"/>
+      <c r="E45" s="131"/>
+      <c r="F45" s="219"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1">
       <c r="A46" s="21"/>
@@ -6398,11 +6392,11 @@
       <c r="F46" s="26"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1">
-      <c r="A47" s="330" t="s">
+      <c r="A47" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="B47" s="331"/>
-      <c r="C47" s="332"/>
+      <c r="B47" s="302"/>
+      <c r="C47" s="308"/>
       <c r="D47" s="78" t="s">
         <v>68</v>
       </c>
@@ -6412,11 +6406,11 @@
       <c r="F47" s="26"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1">
-      <c r="A48" s="330" t="s">
+      <c r="A48" s="301" t="s">
         <v>69</v>
       </c>
-      <c r="B48" s="331"/>
-      <c r="C48" s="332"/>
+      <c r="B48" s="302"/>
+      <c r="C48" s="308"/>
       <c r="D48" s="10"/>
       <c r="E48" s="10" t="s">
         <v>70</v>
@@ -6440,34 +6434,34 @@
       <c r="F50" s="26"/>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1">
-      <c r="A51" s="327"/>
-      <c r="B51" s="328"/>
-      <c r="C51" s="329"/>
-      <c r="D51" s="328" t="s">
+      <c r="A51" s="313"/>
+      <c r="B51" s="314"/>
+      <c r="C51" s="315"/>
+      <c r="D51" s="314" t="s">
         <v>128</v>
       </c>
-      <c r="E51" s="328"/>
-      <c r="F51" s="329"/>
+      <c r="E51" s="314"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1">
-      <c r="A52" s="330" t="s">
+      <c r="A52" s="301" t="s">
         <v>71</v>
       </c>
-      <c r="B52" s="331"/>
-      <c r="C52" s="332"/>
-      <c r="D52" s="331" t="s">
+      <c r="B52" s="302"/>
+      <c r="C52" s="308"/>
+      <c r="D52" s="302" t="s">
         <v>82</v>
       </c>
-      <c r="E52" s="331"/>
-      <c r="F52" s="332"/>
+      <c r="E52" s="302"/>
+      <c r="F52" s="308"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1">
-      <c r="A53" s="338"/>
-      <c r="B53" s="339"/>
-      <c r="C53" s="340"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="340"/>
+      <c r="A53" s="326"/>
+      <c r="B53" s="327"/>
+      <c r="C53" s="328"/>
+      <c r="D53" s="327"/>
+      <c r="E53" s="327"/>
+      <c r="F53" s="328"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1"/>
     <row r="55" spans="1:6" ht="15" customHeight="1"/>
@@ -8597,18 +8591,6 @@
     <row r="18099" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A47:C47"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A2:C2"/>
@@ -8624,6 +8606,18 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0" header="0" footer="0"/>
@@ -8646,591 +8640,591 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="320" t="s">
+      <c r="A1" s="440" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="320"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="321"/>
-      <c r="F1" s="322"/>
-      <c r="G1" s="322"/>
-      <c r="H1" s="323"/>
+      <c r="B1" s="440"/>
+      <c r="C1" s="440"/>
+      <c r="D1" s="440"/>
+      <c r="E1" s="441"/>
+      <c r="F1" s="442"/>
+      <c r="G1" s="442"/>
+      <c r="H1" s="443"/>
     </row>
     <row r="2" spans="1:8" ht="20.25">
-      <c r="A2" s="324" t="s">
+      <c r="A2" s="444" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="324"/>
-      <c r="C2" s="324"/>
-      <c r="D2" s="324"/>
-      <c r="E2" s="314" t="s">
+      <c r="B2" s="444"/>
+      <c r="C2" s="444"/>
+      <c r="D2" s="444"/>
+      <c r="E2" s="445" t="s">
         <v>124</v>
       </c>
-      <c r="F2" s="315"/>
-      <c r="G2" s="315"/>
-      <c r="H2" s="316"/>
+      <c r="F2" s="446"/>
+      <c r="G2" s="446"/>
+      <c r="H2" s="447"/>
     </row>
     <row r="3" spans="1:8" ht="20.25">
-      <c r="A3" s="311" t="s">
+      <c r="A3" s="448" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="312"/>
-      <c r="C3" s="312"/>
-      <c r="D3" s="313"/>
-      <c r="E3" s="314" t="s">
+      <c r="B3" s="449"/>
+      <c r="C3" s="449"/>
+      <c r="D3" s="450"/>
+      <c r="E3" s="445" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="315"/>
-      <c r="G3" s="315"/>
-      <c r="H3" s="316"/>
+      <c r="F3" s="446"/>
+      <c r="G3" s="446"/>
+      <c r="H3" s="447"/>
     </row>
     <row r="4" spans="1:8" ht="20.25">
-      <c r="A4" s="311" t="s">
+      <c r="A4" s="448" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="312"/>
-      <c r="C4" s="312"/>
-      <c r="D4" s="313"/>
-      <c r="E4" s="314" t="s">
+      <c r="B4" s="449"/>
+      <c r="C4" s="449"/>
+      <c r="D4" s="450"/>
+      <c r="E4" s="445" t="s">
         <v>122</v>
       </c>
-      <c r="F4" s="315"/>
-      <c r="G4" s="315"/>
-      <c r="H4" s="316"/>
+      <c r="F4" s="446"/>
+      <c r="G4" s="446"/>
+      <c r="H4" s="447"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="311" t="s">
+      <c r="A5" s="448" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="312"/>
-      <c r="C5" s="312"/>
-      <c r="D5" s="313"/>
-      <c r="E5" s="311" t="s">
+      <c r="B5" s="449"/>
+      <c r="C5" s="449"/>
+      <c r="D5" s="450"/>
+      <c r="E5" s="448" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="312"/>
-      <c r="G5" s="312"/>
-      <c r="H5" s="313"/>
+      <c r="F5" s="449"/>
+      <c r="G5" s="449"/>
+      <c r="H5" s="450"/>
     </row>
     <row r="6" spans="1:8" ht="8.1" customHeight="1">
-      <c r="A6" s="317"/>
-      <c r="B6" s="318"/>
-      <c r="C6" s="318"/>
-      <c r="D6" s="319"/>
-      <c r="E6" s="317"/>
-      <c r="F6" s="318"/>
-      <c r="G6" s="318"/>
-      <c r="H6" s="319"/>
+      <c r="A6" s="451"/>
+      <c r="B6" s="452"/>
+      <c r="C6" s="452"/>
+      <c r="D6" s="453"/>
+      <c r="E6" s="451"/>
+      <c r="F6" s="452"/>
+      <c r="G6" s="452"/>
+      <c r="H6" s="453"/>
     </row>
     <row r="7" spans="1:8" ht="8.1" customHeight="1">
-      <c r="A7" s="150"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="149"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="156"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="148"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="148" t="s">
+      <c r="A8" s="147" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="296"/>
-      <c r="C8" s="157"/>
-      <c r="D8" s="157"/>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="158" t="s">
+      <c r="B8" s="295"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="157" t="s">
         <v>119</v>
       </c>
-      <c r="H8" s="166"/>
+      <c r="H8" s="165"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="148" t="s">
+      <c r="A9" s="147" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="274"/>
-      <c r="C9" s="274"/>
-      <c r="D9" s="159"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="161" t="s">
+      <c r="B9" s="273"/>
+      <c r="C9" s="273"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="160" t="s">
         <v>117</v>
       </c>
-      <c r="H9" s="152"/>
+      <c r="H9" s="151"/>
     </row>
     <row r="10" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A10" s="308" t="s">
+      <c r="A10" s="454" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="308"/>
-      <c r="C10" s="308"/>
-      <c r="D10" s="308"/>
-      <c r="E10" s="308"/>
-      <c r="F10" s="308"/>
-      <c r="G10" s="309" t="s">
+      <c r="B10" s="454"/>
+      <c r="C10" s="454"/>
+      <c r="D10" s="454"/>
+      <c r="E10" s="454"/>
+      <c r="F10" s="454"/>
+      <c r="G10" s="455" t="s">
         <v>115</v>
       </c>
-      <c r="H10" s="309"/>
+      <c r="H10" s="455"/>
     </row>
     <row r="11" spans="1:8" ht="45">
-      <c r="A11" s="146" t="s">
+      <c r="A11" s="145" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="147" t="s">
+      <c r="B11" s="146" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="147" t="s">
+      <c r="C11" s="146" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="146" t="s">
+      <c r="D11" s="145" t="s">
         <v>111</v>
       </c>
-      <c r="E11" s="146" t="s">
+      <c r="E11" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="155" t="s">
+      <c r="F11" s="154" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="146" t="s">
+      <c r="G11" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="146" t="s">
+      <c r="H11" s="145" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
-      <c r="A12" s="177"/>
-      <c r="B12" s="154"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="268"/>
+      <c r="A12" s="176"/>
+      <c r="B12" s="153"/>
+      <c r="C12" s="139"/>
+      <c r="D12" s="267"/>
       <c r="E12" s="81"/>
-      <c r="F12" s="221"/>
+      <c r="F12" s="220"/>
       <c r="G12" s="60"/>
       <c r="H12" s="60"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="177"/>
-      <c r="B13" s="300"/>
-      <c r="C13" s="140"/>
-      <c r="D13" s="297"/>
+      <c r="A13" s="176"/>
+      <c r="B13" s="299"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="296"/>
       <c r="E13" s="81"/>
-      <c r="F13" s="221"/>
+      <c r="F13" s="220"/>
       <c r="G13" s="60"/>
       <c r="H13" s="60"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="177"/>
-      <c r="B14" s="154"/>
+      <c r="A14" s="176"/>
+      <c r="B14" s="153"/>
       <c r="C14" s="64"/>
-      <c r="D14" s="268"/>
+      <c r="D14" s="267"/>
       <c r="E14" s="81"/>
-      <c r="F14" s="210"/>
+      <c r="F14" s="209"/>
       <c r="G14" s="60"/>
       <c r="H14" s="60"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="136"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="275"/>
+      <c r="A15" s="135"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="274"/>
       <c r="E15" s="81"/>
-      <c r="F15" s="228"/>
+      <c r="F15" s="227"/>
       <c r="G15" s="60"/>
       <c r="H15" s="60"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="218"/>
-      <c r="B16" s="145"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="298"/>
-      <c r="E16" s="279"/>
-      <c r="F16" s="228"/>
-      <c r="G16" s="178"/>
-      <c r="H16" s="178"/>
+      <c r="A16" s="217"/>
+      <c r="B16" s="144"/>
+      <c r="C16" s="139"/>
+      <c r="D16" s="297"/>
+      <c r="E16" s="278"/>
+      <c r="F16" s="227"/>
+      <c r="G16" s="177"/>
+      <c r="H16" s="177"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="218"/>
-      <c r="B17" s="145"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="275"/>
-      <c r="E17" s="221"/>
-      <c r="F17" s="228"/>
-      <c r="G17" s="178"/>
-      <c r="H17" s="178"/>
+      <c r="A17" s="217"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="274"/>
+      <c r="E17" s="220"/>
+      <c r="F17" s="227"/>
+      <c r="G17" s="177"/>
+      <c r="H17" s="177"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="218"/>
-      <c r="B18" s="154"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="219"/>
-      <c r="E18" s="280"/>
-      <c r="F18" s="151"/>
-      <c r="G18" s="178"/>
-      <c r="H18" s="178"/>
+      <c r="A18" s="217"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="218"/>
+      <c r="E18" s="279"/>
+      <c r="F18" s="150"/>
+      <c r="G18" s="177"/>
+      <c r="H18" s="177"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="177"/>
-      <c r="B19" s="154"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="279"/>
-      <c r="F19" s="188"/>
-      <c r="G19" s="178"/>
-      <c r="H19" s="178"/>
+      <c r="A19" s="176"/>
+      <c r="B19" s="153"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="218"/>
+      <c r="E19" s="278"/>
+      <c r="F19" s="187"/>
+      <c r="G19" s="177"/>
+      <c r="H19" s="177"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="177"/>
-      <c r="B20" s="154"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="298"/>
-      <c r="E20" s="278"/>
-      <c r="F20" s="188"/>
-      <c r="G20" s="181"/>
-      <c r="H20" s="181"/>
+      <c r="A20" s="176"/>
+      <c r="B20" s="153"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="297"/>
+      <c r="E20" s="277"/>
+      <c r="F20" s="187"/>
+      <c r="G20" s="180"/>
+      <c r="H20" s="180"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
-      <c r="A21" s="227"/>
-      <c r="B21" s="145"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="268"/>
-      <c r="E21" s="281"/>
+      <c r="A21" s="226"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="267"/>
+      <c r="E21" s="280"/>
       <c r="F21" s="82"/>
-      <c r="G21" s="181"/>
-      <c r="H21" s="181"/>
+      <c r="G21" s="180"/>
+      <c r="H21" s="180"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="177"/>
-      <c r="B22" s="154"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="186"/>
-      <c r="E22" s="279"/>
-      <c r="F22" s="221"/>
-      <c r="G22" s="178"/>
-      <c r="H22" s="178"/>
+      <c r="A22" s="176"/>
+      <c r="B22" s="153"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="185"/>
+      <c r="E22" s="278"/>
+      <c r="F22" s="220"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="177"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="227"/>
-      <c r="B23" s="145"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="266"/>
-      <c r="E23" s="260"/>
-      <c r="F23" s="221"/>
-      <c r="G23" s="178"/>
-      <c r="H23" s="178"/>
+      <c r="A23" s="226"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="139"/>
+      <c r="D23" s="265"/>
+      <c r="E23" s="259"/>
+      <c r="F23" s="220"/>
+      <c r="G23" s="177"/>
+      <c r="H23" s="177"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="153"/>
-      <c r="B24" s="145"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="189"/>
-      <c r="E24" s="260"/>
-      <c r="F24" s="221"/>
-      <c r="G24" s="178"/>
-      <c r="H24" s="178"/>
+      <c r="A24" s="152"/>
+      <c r="B24" s="144"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="188"/>
+      <c r="E24" s="259"/>
+      <c r="F24" s="220"/>
+      <c r="G24" s="177"/>
+      <c r="H24" s="177"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="227"/>
-      <c r="B25" s="145"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="243"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="221"/>
-      <c r="G25" s="178"/>
-      <c r="H25" s="178"/>
+      <c r="A25" s="226"/>
+      <c r="B25" s="144"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="242"/>
+      <c r="E25" s="259"/>
+      <c r="F25" s="220"/>
+      <c r="G25" s="177"/>
+      <c r="H25" s="177"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="153"/>
-      <c r="B26" s="145"/>
-      <c r="C26" s="259"/>
-      <c r="D26" s="256"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="247"/>
-      <c r="G26" s="178"/>
-      <c r="H26" s="178"/>
+      <c r="A26" s="152"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="258"/>
+      <c r="D26" s="255"/>
+      <c r="E26" s="259"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="177"/>
+      <c r="H26" s="177"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
-      <c r="A27" s="153"/>
-      <c r="B27" s="145"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="258"/>
-      <c r="E27" s="260"/>
-      <c r="F27" s="221"/>
-      <c r="G27" s="178"/>
-      <c r="H27" s="178"/>
+      <c r="A27" s="152"/>
+      <c r="B27" s="144"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="257"/>
+      <c r="E27" s="259"/>
+      <c r="F27" s="220"/>
+      <c r="G27" s="177"/>
+      <c r="H27" s="177"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="153"/>
-      <c r="B28" s="145"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="253"/>
-      <c r="E28" s="257"/>
-      <c r="F28" s="221"/>
-      <c r="G28" s="178"/>
-      <c r="H28" s="178"/>
+      <c r="A28" s="152"/>
+      <c r="B28" s="144"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="252"/>
+      <c r="E28" s="256"/>
+      <c r="F28" s="220"/>
+      <c r="G28" s="177"/>
+      <c r="H28" s="177"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="153"/>
-      <c r="B29" s="145"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="245"/>
-      <c r="E29" s="252"/>
-      <c r="F29" s="221"/>
-      <c r="G29" s="178"/>
-      <c r="H29" s="178"/>
+      <c r="A29" s="152"/>
+      <c r="B29" s="144"/>
+      <c r="C29" s="139"/>
+      <c r="D29" s="244"/>
+      <c r="E29" s="251"/>
+      <c r="F29" s="220"/>
+      <c r="G29" s="177"/>
+      <c r="H29" s="177"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
-      <c r="A30" s="153"/>
-      <c r="B30" s="145"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="226"/>
-      <c r="E30" s="221"/>
-      <c r="F30" s="221"/>
-      <c r="G30" s="178"/>
-      <c r="H30" s="178"/>
+      <c r="A30" s="152"/>
+      <c r="B30" s="144"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="220"/>
+      <c r="F30" s="220"/>
+      <c r="G30" s="177"/>
+      <c r="H30" s="177"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="153"/>
-      <c r="B31" s="145"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="253"/>
-      <c r="E31" s="221"/>
-      <c r="F31" s="193"/>
-      <c r="G31" s="178"/>
-      <c r="H31" s="192"/>
+      <c r="A31" s="152"/>
+      <c r="B31" s="144"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="252"/>
+      <c r="E31" s="220"/>
+      <c r="F31" s="192"/>
+      <c r="G31" s="177"/>
+      <c r="H31" s="191"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="153"/>
-      <c r="B32" s="145"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="254"/>
-      <c r="E32" s="255"/>
-      <c r="F32" s="193"/>
-      <c r="G32" s="178"/>
-      <c r="H32" s="192"/>
+      <c r="A32" s="152"/>
+      <c r="B32" s="144"/>
+      <c r="C32" s="139"/>
+      <c r="D32" s="253"/>
+      <c r="E32" s="254"/>
+      <c r="F32" s="192"/>
+      <c r="G32" s="177"/>
+      <c r="H32" s="191"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="153"/>
-      <c r="B33" s="145"/>
-      <c r="C33" s="194"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="190"/>
-      <c r="F33" s="193"/>
-      <c r="G33" s="192"/>
-      <c r="H33" s="192"/>
+      <c r="A33" s="152"/>
+      <c r="B33" s="144"/>
+      <c r="C33" s="193"/>
+      <c r="D33" s="162"/>
+      <c r="E33" s="189"/>
+      <c r="F33" s="192"/>
+      <c r="G33" s="191"/>
+      <c r="H33" s="191"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
-      <c r="A34" s="153"/>
-      <c r="B34" s="145"/>
-      <c r="C34" s="194"/>
-      <c r="D34" s="163"/>
-      <c r="E34" s="190"/>
-      <c r="F34" s="193"/>
-      <c r="G34" s="192"/>
-      <c r="H34" s="192"/>
+      <c r="A34" s="152"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="193"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="189"/>
+      <c r="F34" s="192"/>
+      <c r="G34" s="191"/>
+      <c r="H34" s="191"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="153"/>
-      <c r="B35" s="145"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="189"/>
-      <c r="E35" s="190"/>
-      <c r="F35" s="193"/>
-      <c r="G35" s="192"/>
-      <c r="H35" s="192"/>
+      <c r="A35" s="152"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="193"/>
+      <c r="D35" s="188"/>
+      <c r="E35" s="189"/>
+      <c r="F35" s="192"/>
+      <c r="G35" s="191"/>
+      <c r="H35" s="191"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="153"/>
-      <c r="B36" s="145"/>
-      <c r="C36" s="145"/>
-      <c r="D36" s="191"/>
-      <c r="E36" s="165"/>
-      <c r="F36" s="145"/>
-      <c r="G36" s="174"/>
-      <c r="H36" s="174"/>
+      <c r="A36" s="152"/>
+      <c r="B36" s="144"/>
+      <c r="C36" s="144"/>
+      <c r="D36" s="190"/>
+      <c r="E36" s="164"/>
+      <c r="F36" s="144"/>
+      <c r="G36" s="173"/>
+      <c r="H36" s="173"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="153"/>
-      <c r="B37" s="145"/>
-      <c r="C37" s="145"/>
-      <c r="D37" s="164"/>
-      <c r="E37" s="165"/>
-      <c r="F37" s="145"/>
-      <c r="G37" s="174"/>
-      <c r="H37" s="174"/>
+      <c r="A37" s="152"/>
+      <c r="B37" s="144"/>
+      <c r="C37" s="144"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="164"/>
+      <c r="F37" s="144"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="173"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="153"/>
-      <c r="B38" s="145"/>
-      <c r="C38" s="145"/>
-      <c r="D38" s="164"/>
-      <c r="E38" s="165"/>
-      <c r="F38" s="145"/>
-      <c r="G38" s="174"/>
-      <c r="H38" s="174"/>
+      <c r="A38" s="152"/>
+      <c r="B38" s="144"/>
+      <c r="C38" s="144"/>
+      <c r="D38" s="163"/>
+      <c r="E38" s="164"/>
+      <c r="F38" s="144"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="173"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="153"/>
-      <c r="B39" s="145"/>
-      <c r="C39" s="145"/>
-      <c r="D39" s="164"/>
-      <c r="E39" s="165"/>
-      <c r="F39" s="145"/>
-      <c r="G39" s="144"/>
-      <c r="H39" s="178">
+      <c r="A39" s="152"/>
+      <c r="B39" s="144"/>
+      <c r="C39" s="144"/>
+      <c r="D39" s="163"/>
+      <c r="E39" s="164"/>
+      <c r="F39" s="144"/>
+      <c r="G39" s="143"/>
+      <c r="H39" s="177">
         <f>SUM(H12:H38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="143" t="s">
+      <c r="A40" s="142" t="s">
         <v>109</v>
       </c>
-      <c r="B40" s="143"/>
-      <c r="C40" s="143"/>
-      <c r="D40" s="143"/>
-      <c r="E40" s="310" t="s">
+      <c r="B40" s="142"/>
+      <c r="C40" s="142"/>
+      <c r="D40" s="142"/>
+      <c r="E40" s="456" t="s">
         <v>108</v>
       </c>
-      <c r="F40" s="310"/>
-      <c r="G40" s="310"/>
-      <c r="H40" s="310"/>
+      <c r="F40" s="456"/>
+      <c r="G40" s="456"/>
+      <c r="H40" s="456"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="301"/>
-      <c r="B41" s="301"/>
-      <c r="C41" s="301"/>
-      <c r="D41" s="301"/>
-      <c r="E41" s="301"/>
-      <c r="F41" s="301"/>
-      <c r="G41" s="301"/>
-      <c r="H41" s="301"/>
+      <c r="A41" s="457"/>
+      <c r="B41" s="457"/>
+      <c r="C41" s="457"/>
+      <c r="D41" s="457"/>
+      <c r="E41" s="457"/>
+      <c r="F41" s="457"/>
+      <c r="G41" s="457"/>
+      <c r="H41" s="457"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="301" t="s">
+      <c r="A42" s="457" t="s">
         <v>107</v>
       </c>
-      <c r="B42" s="301"/>
-      <c r="C42" s="301"/>
-      <c r="D42" s="301"/>
-      <c r="E42" s="301"/>
-      <c r="F42" s="301"/>
-      <c r="G42" s="301"/>
-      <c r="H42" s="301"/>
+      <c r="B42" s="457"/>
+      <c r="C42" s="457"/>
+      <c r="D42" s="457"/>
+      <c r="E42" s="457"/>
+      <c r="F42" s="457"/>
+      <c r="G42" s="457"/>
+      <c r="H42" s="457"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="302" t="s">
+      <c r="A43" s="458" t="s">
         <v>128</v>
       </c>
-      <c r="B43" s="303"/>
-      <c r="C43" s="303"/>
-      <c r="D43" s="304"/>
-      <c r="E43" s="156" t="s">
+      <c r="B43" s="459"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="155" t="s">
         <v>106</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="142" t="s">
+      <c r="H43" s="141" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="305" t="s">
+      <c r="A44" s="461" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="305"/>
-      <c r="C44" s="305"/>
-      <c r="D44" s="305"/>
-      <c r="E44" s="306" t="s">
+      <c r="B44" s="461"/>
+      <c r="C44" s="461"/>
+      <c r="D44" s="461"/>
+      <c r="E44" s="462" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="307"/>
-      <c r="G44" s="307"/>
-      <c r="H44" s="141" t="s">
+      <c r="F44" s="463"/>
+      <c r="G44" s="463"/>
+      <c r="H44" s="140" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="195"/>
-      <c r="B45" s="195"/>
-      <c r="C45" s="195"/>
-      <c r="D45" s="195"/>
-      <c r="E45" s="195"/>
-      <c r="F45" s="195"/>
-      <c r="G45" s="195"/>
-      <c r="H45" s="195"/>
+      <c r="A45" s="194"/>
+      <c r="B45" s="194"/>
+      <c r="C45" s="194"/>
+      <c r="D45" s="194"/>
+      <c r="E45" s="194"/>
+      <c r="F45" s="194"/>
+      <c r="G45" s="194"/>
+      <c r="H45" s="194"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="195"/>
-      <c r="B46" s="195"/>
-      <c r="C46" s="195"/>
-      <c r="D46" s="195"/>
-      <c r="E46" s="195"/>
-      <c r="F46" s="195"/>
-      <c r="G46" s="195"/>
-      <c r="H46" s="195"/>
+      <c r="A46" s="194"/>
+      <c r="B46" s="194"/>
+      <c r="C46" s="194"/>
+      <c r="D46" s="194"/>
+      <c r="E46" s="194"/>
+      <c r="F46" s="194"/>
+      <c r="G46" s="194"/>
+      <c r="H46" s="194"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="195"/>
-      <c r="B47" s="195"/>
-      <c r="C47" s="195"/>
-      <c r="D47" s="195"/>
-      <c r="E47" s="195"/>
-      <c r="F47" s="195"/>
-      <c r="G47" s="195"/>
-      <c r="H47" s="195"/>
+      <c r="A47" s="194"/>
+      <c r="B47" s="194"/>
+      <c r="C47" s="194"/>
+      <c r="D47" s="194"/>
+      <c r="E47" s="194"/>
+      <c r="F47" s="194"/>
+      <c r="G47" s="194"/>
+      <c r="H47" s="194"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="195"/>
-      <c r="B48" s="195"/>
-      <c r="C48" s="195"/>
-      <c r="D48" s="195"/>
-      <c r="E48" s="195"/>
-      <c r="F48" s="195"/>
-      <c r="G48" s="195"/>
-      <c r="H48" s="195"/>
+      <c r="A48" s="194"/>
+      <c r="B48" s="194"/>
+      <c r="C48" s="194"/>
+      <c r="D48" s="194"/>
+      <c r="E48" s="194"/>
+      <c r="F48" s="194"/>
+      <c r="G48" s="194"/>
+      <c r="H48" s="194"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="195"/>
-      <c r="B49" s="195"/>
-      <c r="C49" s="195"/>
-      <c r="D49" s="195"/>
-      <c r="E49" s="195"/>
-      <c r="F49" s="195"/>
-      <c r="G49" s="195"/>
-      <c r="H49" s="195"/>
+      <c r="A49" s="194"/>
+      <c r="B49" s="194"/>
+      <c r="C49" s="194"/>
+      <c r="D49" s="194"/>
+      <c r="E49" s="194"/>
+      <c r="F49" s="194"/>
+      <c r="G49" s="194"/>
+      <c r="H49" s="194"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="195"/>
-      <c r="B50" s="195"/>
-      <c r="C50" s="195"/>
-      <c r="D50" s="195"/>
-      <c r="E50" s="195"/>
-      <c r="F50" s="195"/>
-      <c r="G50" s="195"/>
-      <c r="H50" s="195"/>
+      <c r="A50" s="194"/>
+      <c r="B50" s="194"/>
+      <c r="C50" s="194"/>
+      <c r="D50" s="194"/>
+      <c r="E50" s="194"/>
+      <c r="F50" s="194"/>
+      <c r="G50" s="194"/>
+      <c r="H50" s="194"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="195"/>
-      <c r="B51" s="195"/>
-      <c r="C51" s="195"/>
-      <c r="D51" s="195"/>
-      <c r="E51" s="195"/>
-      <c r="F51" s="195"/>
-      <c r="G51" s="195"/>
-      <c r="H51" s="195"/>
+      <c r="A51" s="194"/>
+      <c r="B51" s="194"/>
+      <c r="C51" s="194"/>
+      <c r="D51" s="194"/>
+      <c r="E51" s="194"/>
+      <c r="F51" s="194"/>
+      <c r="G51" s="194"/>
+      <c r="H51" s="194"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="195"/>
-      <c r="B52" s="195"/>
-      <c r="C52" s="195"/>
-      <c r="D52" s="195"/>
-      <c r="E52" s="195"/>
-      <c r="F52" s="195"/>
-      <c r="G52" s="195"/>
-      <c r="H52" s="195"/>
+      <c r="A52" s="194"/>
+      <c r="B52" s="194"/>
+      <c r="C52" s="194"/>
+      <c r="D52" s="194"/>
+      <c r="E52" s="194"/>
+      <c r="F52" s="194"/>
+      <c r="G52" s="194"/>
+      <c r="H52" s="194"/>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1"/>
     <row r="113" ht="15" customHeight="1"/>
@@ -9240,28 +9234,28 @@
     <row r="187" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:H6"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:G44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.98425196850393704" bottom="0.23622047244094499" header="3.9370078740157501E-2" footer="3.9370078740157501E-2"/>
@@ -9288,129 +9282,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="443" t="s">
+      <c r="A1" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="443"/>
-      <c r="C1" s="443"/>
-      <c r="D1" s="443"/>
-      <c r="E1" s="464"/>
-      <c r="F1" s="465"/>
-      <c r="G1" s="465"/>
-      <c r="H1" s="465"/>
-      <c r="I1" s="466"/>
+      <c r="B1" s="324"/>
+      <c r="C1" s="324"/>
+      <c r="D1" s="324"/>
+      <c r="E1" s="495"/>
+      <c r="F1" s="496"/>
+      <c r="G1" s="496"/>
+      <c r="H1" s="496"/>
+      <c r="I1" s="497"/>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1">
-      <c r="A2" s="450" t="s">
+      <c r="A2" s="428" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="450"/>
-      <c r="C2" s="450"/>
-      <c r="D2" s="450"/>
-      <c r="E2" s="456" t="s">
+      <c r="B2" s="428"/>
+      <c r="C2" s="428"/>
+      <c r="D2" s="428"/>
+      <c r="E2" s="434" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="457"/>
-      <c r="G2" s="457"/>
-      <c r="H2" s="457"/>
-      <c r="I2" s="458"/>
+      <c r="F2" s="435"/>
+      <c r="G2" s="435"/>
+      <c r="H2" s="435"/>
+      <c r="I2" s="436"/>
     </row>
     <row r="3" spans="1:9" ht="21" customHeight="1">
-      <c r="A3" s="467"/>
-      <c r="B3" s="467"/>
-      <c r="C3" s="467"/>
-      <c r="D3" s="467"/>
-      <c r="E3" s="456" t="s">
+      <c r="A3" s="498"/>
+      <c r="B3" s="498"/>
+      <c r="C3" s="498"/>
+      <c r="D3" s="498"/>
+      <c r="E3" s="434" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="457"/>
-      <c r="G3" s="457"/>
-      <c r="H3" s="457"/>
-      <c r="I3" s="458"/>
+      <c r="F3" s="435"/>
+      <c r="G3" s="435"/>
+      <c r="H3" s="435"/>
+      <c r="I3" s="436"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="468" t="s">
+      <c r="A4" s="484" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="468"/>
-      <c r="C4" s="468"/>
-      <c r="D4" s="468"/>
-      <c r="E4" s="469"/>
-      <c r="F4" s="470"/>
-      <c r="G4" s="470"/>
-      <c r="H4" s="470"/>
-      <c r="I4" s="471"/>
+      <c r="B4" s="484"/>
+      <c r="C4" s="484"/>
+      <c r="D4" s="484"/>
+      <c r="E4" s="485"/>
+      <c r="F4" s="486"/>
+      <c r="G4" s="486"/>
+      <c r="H4" s="486"/>
+      <c r="I4" s="487"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
-      <c r="A5" s="468" t="s">
+      <c r="A5" s="484" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="468"/>
-      <c r="C5" s="468"/>
-      <c r="D5" s="468"/>
-      <c r="E5" s="472" t="s">
+      <c r="B5" s="484"/>
+      <c r="C5" s="484"/>
+      <c r="D5" s="484"/>
+      <c r="E5" s="488" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="473"/>
-      <c r="G5" s="473"/>
-      <c r="H5" s="473"/>
-      <c r="I5" s="474"/>
+      <c r="F5" s="489"/>
+      <c r="G5" s="489"/>
+      <c r="H5" s="489"/>
+      <c r="I5" s="490"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
-      <c r="A6" s="475" t="s">
+      <c r="A6" s="491" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="475"/>
-      <c r="C6" s="475"/>
-      <c r="D6" s="475"/>
-      <c r="E6" s="476"/>
-      <c r="F6" s="477"/>
-      <c r="G6" s="477"/>
-      <c r="H6" s="477"/>
-      <c r="I6" s="478"/>
+      <c r="B6" s="491"/>
+      <c r="C6" s="491"/>
+      <c r="D6" s="491"/>
+      <c r="E6" s="492"/>
+      <c r="F6" s="493"/>
+      <c r="G6" s="493"/>
+      <c r="H6" s="493"/>
+      <c r="I6" s="494"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="389"/>
-      <c r="C7" s="479"/>
+      <c r="B7" s="395"/>
+      <c r="C7" s="478"/>
       <c r="D7" s="10"/>
       <c r="E7" s="28"/>
       <c r="F7" s="10" t="s">
         <v>88</v>
       </c>
       <c r="G7" s="10"/>
-      <c r="H7" s="480"/>
-      <c r="I7" s="481"/>
+      <c r="H7" s="479"/>
+      <c r="I7" s="480"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="482"/>
-      <c r="C8" s="483"/>
+      <c r="B8" s="481"/>
+      <c r="C8" s="482"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="433" t="s">
+      <c r="F8" s="348" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="433"/>
-      <c r="H8" s="484"/>
-      <c r="I8" s="382"/>
+      <c r="G8" s="348"/>
+      <c r="H8" s="483"/>
+      <c r="I8" s="319"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="396"/>
-      <c r="B9" s="485"/>
-      <c r="C9" s="485"/>
-      <c r="D9" s="485"/>
-      <c r="E9" s="485"/>
-      <c r="F9" s="485"/>
-      <c r="G9" s="397"/>
-      <c r="H9" s="486" t="s">
+      <c r="A9" s="377"/>
+      <c r="B9" s="474"/>
+      <c r="C9" s="474"/>
+      <c r="D9" s="474"/>
+      <c r="E9" s="474"/>
+      <c r="F9" s="474"/>
+      <c r="G9" s="378"/>
+      <c r="H9" s="475" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="486"/>
+      <c r="I9" s="475"/>
     </row>
     <row r="10" spans="1:9" ht="33.75">
       <c r="A10" s="6" t="s">
@@ -9422,14 +9416,14 @@
       <c r="C10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="489" t="s">
+      <c r="D10" s="464" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="490"/>
+      <c r="E10" s="465"/>
       <c r="F10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="173" t="s">
+      <c r="G10" s="172" t="s">
         <v>77</v>
       </c>
       <c r="H10" s="6" t="s">
@@ -9440,81 +9434,81 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
-      <c r="A11" s="240"/>
-      <c r="B11" s="170"/>
+      <c r="A11" s="239"/>
+      <c r="B11" s="169"/>
       <c r="C11" s="48"/>
       <c r="D11" s="8"/>
       <c r="E11" s="104"/>
-      <c r="F11" s="221"/>
-      <c r="G11" s="221"/>
-      <c r="H11" s="178"/>
-      <c r="I11" s="178"/>
+      <c r="F11" s="220"/>
+      <c r="G11" s="220"/>
+      <c r="H11" s="177"/>
+      <c r="I11" s="177"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
-      <c r="A12" s="123"/>
+      <c r="A12" s="122"/>
       <c r="B12" s="51"/>
       <c r="C12" s="56"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="221"/>
-      <c r="G12" s="221"/>
-      <c r="H12" s="178"/>
-      <c r="I12" s="178"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="220"/>
+      <c r="G12" s="220"/>
+      <c r="H12" s="177"/>
+      <c r="I12" s="177"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="69"/>
       <c r="B13" s="51"/>
       <c r="C13" s="56"/>
-      <c r="D13" s="268"/>
-      <c r="E13" s="283"/>
-      <c r="F13" s="221"/>
-      <c r="G13" s="210"/>
-      <c r="H13" s="178"/>
-      <c r="I13" s="178"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="282"/>
+      <c r="F13" s="220"/>
+      <c r="G13" s="209"/>
+      <c r="H13" s="177"/>
+      <c r="I13" s="177"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="29"/>
       <c r="B14" s="51"/>
       <c r="C14" s="56"/>
-      <c r="D14" s="297"/>
-      <c r="E14" s="276"/>
-      <c r="F14" s="221"/>
-      <c r="G14" s="221"/>
-      <c r="H14" s="178"/>
-      <c r="I14" s="178"/>
+      <c r="D14" s="296"/>
+      <c r="E14" s="275"/>
+      <c r="F14" s="220"/>
+      <c r="G14" s="220"/>
+      <c r="H14" s="177"/>
+      <c r="I14" s="177"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="62"/>
       <c r="B15" s="13"/>
       <c r="C15" s="56"/>
-      <c r="D15" s="268"/>
-      <c r="E15" s="283"/>
-      <c r="F15" s="221"/>
-      <c r="G15" s="228"/>
-      <c r="H15" s="178"/>
-      <c r="I15" s="178"/>
+      <c r="D15" s="267"/>
+      <c r="E15" s="282"/>
+      <c r="F15" s="220"/>
+      <c r="G15" s="227"/>
+      <c r="H15" s="177"/>
+      <c r="I15" s="177"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="29"/>
       <c r="B16" s="13"/>
       <c r="C16" s="56"/>
-      <c r="D16" s="275"/>
-      <c r="E16" s="276"/>
-      <c r="F16" s="221"/>
-      <c r="G16" s="228"/>
-      <c r="H16" s="178"/>
-      <c r="I16" s="178"/>
+      <c r="D16" s="274"/>
+      <c r="E16" s="275"/>
+      <c r="F16" s="220"/>
+      <c r="G16" s="227"/>
+      <c r="H16" s="177"/>
+      <c r="I16" s="177"/>
     </row>
     <row r="17" spans="1:17" ht="15" customHeight="1">
-      <c r="A17" s="175"/>
+      <c r="A17" s="174"/>
       <c r="B17" s="51"/>
       <c r="C17" s="56"/>
-      <c r="D17" s="403"/>
-      <c r="E17" s="404"/>
-      <c r="F17" s="221"/>
-      <c r="G17" s="228"/>
-      <c r="H17" s="178"/>
-      <c r="I17" s="178"/>
+      <c r="D17" s="311"/>
+      <c r="E17" s="312"/>
+      <c r="F17" s="220"/>
+      <c r="G17" s="227"/>
+      <c r="H17" s="177"/>
+      <c r="I17" s="177"/>
       <c r="L17" t="s">
         <v>84</v>
       </c>
@@ -9523,34 +9517,34 @@
       <c r="A18" s="29"/>
       <c r="B18" s="51"/>
       <c r="C18" s="56"/>
-      <c r="D18" s="219"/>
-      <c r="E18" s="199"/>
-      <c r="F18" s="221"/>
-      <c r="G18" s="228"/>
-      <c r="H18" s="178"/>
-      <c r="I18" s="178"/>
+      <c r="D18" s="218"/>
+      <c r="E18" s="198"/>
+      <c r="F18" s="220"/>
+      <c r="G18" s="227"/>
+      <c r="H18" s="177"/>
+      <c r="I18" s="177"/>
     </row>
     <row r="19" spans="1:17" ht="15" customHeight="1">
       <c r="A19" s="62"/>
       <c r="B19" s="108"/>
       <c r="C19" s="56"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="241"/>
-      <c r="F19" s="221"/>
-      <c r="G19" s="272"/>
-      <c r="H19" s="178"/>
-      <c r="I19" s="178"/>
+      <c r="D19" s="218"/>
+      <c r="E19" s="240"/>
+      <c r="F19" s="220"/>
+      <c r="G19" s="271"/>
+      <c r="H19" s="177"/>
+      <c r="I19" s="177"/>
     </row>
     <row r="20" spans="1:17" ht="15" customHeight="1">
       <c r="A20" s="29"/>
       <c r="B20" s="51"/>
       <c r="C20" s="56"/>
-      <c r="D20" s="268"/>
-      <c r="E20" s="282"/>
-      <c r="F20" s="221"/>
-      <c r="G20" s="221"/>
-      <c r="H20" s="178"/>
-      <c r="I20" s="178"/>
+      <c r="D20" s="267"/>
+      <c r="E20" s="281"/>
+      <c r="F20" s="220"/>
+      <c r="G20" s="220"/>
+      <c r="H20" s="177"/>
+      <c r="I20" s="177"/>
       <c r="L20" t="s">
         <v>103</v>
       </c>
@@ -9559,45 +9553,45 @@
       <c r="A21" s="29"/>
       <c r="B21" s="51"/>
       <c r="C21" s="56"/>
-      <c r="D21" s="186"/>
-      <c r="E21" s="270"/>
-      <c r="F21" s="221"/>
-      <c r="G21" s="221"/>
-      <c r="H21" s="178"/>
-      <c r="I21" s="178"/>
+      <c r="D21" s="185"/>
+      <c r="E21" s="269"/>
+      <c r="F21" s="220"/>
+      <c r="G21" s="220"/>
+      <c r="H21" s="177"/>
+      <c r="I21" s="177"/>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="51"/>
       <c r="C22" s="56"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="221"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="178"/>
-      <c r="I22" s="178"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="220"/>
+      <c r="G22" s="243"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="177"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1">
       <c r="A23" s="29"/>
       <c r="B23" s="51"/>
       <c r="C23" s="56"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="139"/>
-      <c r="F23" s="221"/>
-      <c r="G23" s="180"/>
-      <c r="H23" s="178"/>
-      <c r="I23" s="178"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="220"/>
+      <c r="G23" s="179"/>
+      <c r="H23" s="177"/>
+      <c r="I23" s="177"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1">
       <c r="A24" s="29"/>
       <c r="B24" s="51"/>
       <c r="C24" s="56"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="241"/>
-      <c r="F24" s="221"/>
-      <c r="G24" s="180"/>
-      <c r="H24" s="178"/>
-      <c r="I24" s="178"/>
+      <c r="E24" s="240"/>
+      <c r="F24" s="220"/>
+      <c r="G24" s="179"/>
+      <c r="H24" s="177"/>
+      <c r="I24" s="177"/>
       <c r="Q24" t="s">
         <v>84</v>
       </c>
@@ -9607,175 +9601,175 @@
       <c r="B25" s="51"/>
       <c r="C25" s="56"/>
       <c r="D25" s="8"/>
-      <c r="E25" s="241"/>
-      <c r="F25" s="221"/>
-      <c r="G25" s="180"/>
-      <c r="H25" s="178"/>
-      <c r="I25" s="178"/>
+      <c r="E25" s="240"/>
+      <c r="F25" s="220"/>
+      <c r="G25" s="179"/>
+      <c r="H25" s="177"/>
+      <c r="I25" s="177"/>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="51"/>
       <c r="C26" s="56"/>
-      <c r="D26" s="219"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="221"/>
-      <c r="G26" s="180"/>
-      <c r="H26" s="178"/>
-      <c r="I26" s="178"/>
+      <c r="D26" s="218"/>
+      <c r="E26" s="240"/>
+      <c r="F26" s="220"/>
+      <c r="G26" s="179"/>
+      <c r="H26" s="177"/>
+      <c r="I26" s="177"/>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1">
       <c r="A27" s="29"/>
       <c r="B27" s="51"/>
       <c r="C27" s="56"/>
-      <c r="D27" s="219"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="221"/>
-      <c r="G27" s="180"/>
-      <c r="H27" s="178"/>
-      <c r="I27" s="178"/>
+      <c r="D27" s="218"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="220"/>
+      <c r="G27" s="179"/>
+      <c r="H27" s="177"/>
+      <c r="I27" s="177"/>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="51"/>
       <c r="C28" s="56"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="282"/>
-      <c r="F28" s="221"/>
-      <c r="G28" s="180"/>
-      <c r="H28" s="178"/>
-      <c r="I28" s="178"/>
+      <c r="E28" s="281"/>
+      <c r="F28" s="220"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="177"/>
+      <c r="I28" s="177"/>
     </row>
     <row r="29" spans="1:17" ht="15" customHeight="1">
       <c r="A29" s="29"/>
       <c r="B29" s="51"/>
       <c r="C29" s="56"/>
-      <c r="D29" s="219"/>
+      <c r="D29" s="218"/>
       <c r="E29" s="105"/>
-      <c r="F29" s="221"/>
-      <c r="G29" s="180"/>
-      <c r="H29" s="178"/>
-      <c r="I29" s="178"/>
+      <c r="F29" s="220"/>
+      <c r="G29" s="179"/>
+      <c r="H29" s="177"/>
+      <c r="I29" s="177"/>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="51"/>
       <c r="C30" s="56"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="242"/>
-      <c r="F30" s="221"/>
-      <c r="G30" s="180"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="178"/>
+      <c r="E30" s="241"/>
+      <c r="F30" s="220"/>
+      <c r="G30" s="179"/>
+      <c r="H30" s="177"/>
+      <c r="I30" s="177"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1">
       <c r="A31" s="29"/>
       <c r="B31" s="51"/>
       <c r="C31" s="56"/>
-      <c r="D31" s="497"/>
-      <c r="E31" s="498"/>
-      <c r="F31" s="221"/>
-      <c r="G31" s="180"/>
-      <c r="H31" s="178"/>
-      <c r="I31" s="178"/>
+      <c r="D31" s="472"/>
+      <c r="E31" s="473"/>
+      <c r="F31" s="220"/>
+      <c r="G31" s="179"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="177"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="51"/>
       <c r="C32" s="56"/>
-      <c r="D32" s="189"/>
-      <c r="E32" s="134"/>
-      <c r="F32" s="221"/>
-      <c r="G32" s="228"/>
-      <c r="H32" s="178"/>
-      <c r="I32" s="178"/>
+      <c r="D32" s="188"/>
+      <c r="E32" s="133"/>
+      <c r="F32" s="220"/>
+      <c r="G32" s="227"/>
+      <c r="H32" s="177"/>
+      <c r="I32" s="177"/>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1">
       <c r="A33" s="29"/>
       <c r="B33" s="51"/>
       <c r="C33" s="56"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="134"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="228"/>
-      <c r="H33" s="178"/>
-      <c r="I33" s="178"/>
+      <c r="D33" s="162"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="178"/>
+      <c r="G33" s="227"/>
+      <c r="H33" s="177"/>
+      <c r="I33" s="177"/>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="51"/>
       <c r="C34" s="56"/>
-      <c r="D34" s="189"/>
-      <c r="E34" s="134"/>
-      <c r="F34" s="221"/>
-      <c r="G34" s="228"/>
-      <c r="H34" s="178"/>
-      <c r="I34" s="178"/>
+      <c r="D34" s="188"/>
+      <c r="E34" s="133"/>
+      <c r="F34" s="220"/>
+      <c r="G34" s="227"/>
+      <c r="H34" s="177"/>
+      <c r="I34" s="177"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1">
       <c r="A35" s="29"/>
       <c r="B35" s="51"/>
       <c r="C35" s="56"/>
       <c r="D35" s="71"/>
-      <c r="E35" s="134"/>
-      <c r="F35" s="221"/>
-      <c r="G35" s="228"/>
-      <c r="H35" s="178"/>
-      <c r="I35" s="178"/>
+      <c r="E35" s="133"/>
+      <c r="F35" s="220"/>
+      <c r="G35" s="227"/>
+      <c r="H35" s="177"/>
+      <c r="I35" s="177"/>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="51"/>
       <c r="C36" s="56"/>
-      <c r="D36" s="189"/>
-      <c r="E36" s="138"/>
-      <c r="F36" s="221"/>
-      <c r="G36" s="228"/>
-      <c r="H36" s="178"/>
-      <c r="I36" s="178"/>
+      <c r="D36" s="188"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="220"/>
+      <c r="G36" s="227"/>
+      <c r="H36" s="177"/>
+      <c r="I36" s="177"/>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1">
       <c r="A37" s="29"/>
       <c r="B37" s="51"/>
       <c r="C37" s="56"/>
-      <c r="D37" s="189"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="221"/>
-      <c r="G37" s="228"/>
-      <c r="H37" s="178"/>
-      <c r="I37" s="178"/>
+      <c r="D37" s="188"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="220"/>
+      <c r="G37" s="227"/>
+      <c r="H37" s="177"/>
+      <c r="I37" s="177"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="51"/>
       <c r="C38" s="56"/>
-      <c r="D38" s="243"/>
-      <c r="E38" s="117"/>
-      <c r="F38" s="221"/>
-      <c r="G38" s="228"/>
-      <c r="H38" s="178"/>
-      <c r="I38" s="178"/>
+      <c r="D38" s="242"/>
+      <c r="E38" s="116"/>
+      <c r="F38" s="220"/>
+      <c r="G38" s="227"/>
+      <c r="H38" s="177"/>
+      <c r="I38" s="177"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1">
       <c r="A39" s="29"/>
       <c r="B39" s="51"/>
       <c r="C39" s="56"/>
-      <c r="D39" s="189"/>
+      <c r="D39" s="188"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="221"/>
-      <c r="G39" s="228"/>
-      <c r="H39" s="178"/>
-      <c r="I39" s="178"/>
+      <c r="F39" s="220"/>
+      <c r="G39" s="227"/>
+      <c r="H39" s="177"/>
+      <c r="I39" s="177"/>
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="51"/>
       <c r="C40" s="56"/>
       <c r="D40" s="57"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="131"/>
-      <c r="G40" s="130"/>
-      <c r="H40" s="178"/>
+      <c r="E40" s="116"/>
+      <c r="F40" s="130"/>
+      <c r="G40" s="129"/>
+      <c r="H40" s="177"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1">
@@ -9784,30 +9778,30 @@
       <c r="C41" s="56"/>
       <c r="D41" s="44"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="491" t="s">
+      <c r="F41" s="466" t="s">
         <v>104</v>
       </c>
-      <c r="G41" s="492"/>
-      <c r="H41" s="493"/>
-      <c r="I41" s="178">
+      <c r="G41" s="467"/>
+      <c r="H41" s="468"/>
+      <c r="I41" s="177">
         <f>SUM(I11:I40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="494" t="s">
+      <c r="A42" s="469" t="s">
         <v>78</v>
       </c>
-      <c r="B42" s="495"/>
+      <c r="B42" s="470"/>
       <c r="C42" s="15"/>
       <c r="D42" s="11"/>
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
-      <c r="G42" s="494" t="s">
+      <c r="G42" s="469" t="s">
         <v>78</v>
       </c>
-      <c r="H42" s="496"/>
-      <c r="I42" s="495"/>
+      <c r="H42" s="471"/>
+      <c r="I42" s="470"/>
     </row>
     <row r="43" spans="1:13" ht="22.5">
       <c r="A43" s="79" t="s">
@@ -9829,7 +9823,7 @@
       <c r="I43" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="M43" s="118"/>
+      <c r="M43" s="117"/>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="79"/>
@@ -9841,7 +9835,7 @@
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
-      <c r="M44" s="118"/>
+      <c r="M44" s="117"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="29"/>
@@ -9877,82 +9871,82 @@
       <c r="I47" s="59"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="171"/>
-      <c r="B48" s="172"/>
-      <c r="C48" s="172"/>
+      <c r="A48" s="170"/>
+      <c r="B48" s="171"/>
+      <c r="C48" s="171"/>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
-      <c r="F48" s="168"/>
-      <c r="G48" s="169"/>
+      <c r="F48" s="167"/>
+      <c r="G48" s="168"/>
       <c r="H48" s="67"/>
       <c r="I48" s="68"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="330"/>
-      <c r="B49" s="331"/>
-      <c r="C49" s="331"/>
-      <c r="D49" s="331"/>
-      <c r="E49" s="332"/>
-      <c r="F49" s="330"/>
-      <c r="G49" s="331"/>
-      <c r="H49" s="331"/>
-      <c r="I49" s="332"/>
+      <c r="A49" s="301"/>
+      <c r="B49" s="302"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="308"/>
+      <c r="F49" s="301"/>
+      <c r="G49" s="302"/>
+      <c r="H49" s="302"/>
+      <c r="I49" s="308"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="330"/>
-      <c r="B50" s="331"/>
-      <c r="C50" s="331"/>
-      <c r="D50" s="331"/>
-      <c r="E50" s="332"/>
-      <c r="F50" s="330"/>
-      <c r="G50" s="331"/>
-      <c r="H50" s="331"/>
-      <c r="I50" s="332"/>
+      <c r="A50" s="301"/>
+      <c r="B50" s="302"/>
+      <c r="C50" s="302"/>
+      <c r="D50" s="302"/>
+      <c r="E50" s="308"/>
+      <c r="F50" s="301"/>
+      <c r="G50" s="302"/>
+      <c r="H50" s="302"/>
+      <c r="I50" s="308"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="327" t="s">
+      <c r="A51" s="313" t="s">
         <v>90</v>
       </c>
-      <c r="B51" s="328"/>
-      <c r="C51" s="328"/>
-      <c r="D51" s="328"/>
-      <c r="E51" s="329"/>
-      <c r="F51" s="487" t="s">
+      <c r="B51" s="314"/>
+      <c r="C51" s="314"/>
+      <c r="D51" s="314"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="476" t="s">
         <v>96</v>
       </c>
-      <c r="G51" s="488"/>
-      <c r="H51" s="488"/>
-      <c r="I51" s="167" t="s">
+      <c r="G51" s="477"/>
+      <c r="H51" s="477"/>
+      <c r="I51" s="166" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="330" t="s">
+      <c r="A52" s="301" t="s">
         <v>34</v>
       </c>
-      <c r="B52" s="331"/>
-      <c r="C52" s="331"/>
-      <c r="D52" s="331"/>
-      <c r="E52" s="332"/>
-      <c r="F52" s="330" t="s">
+      <c r="B52" s="302"/>
+      <c r="C52" s="302"/>
+      <c r="D52" s="302"/>
+      <c r="E52" s="308"/>
+      <c r="F52" s="301" t="s">
         <v>80</v>
       </c>
-      <c r="G52" s="331"/>
-      <c r="H52" s="331"/>
-      <c r="I52" s="167" t="s">
+      <c r="G52" s="302"/>
+      <c r="H52" s="302"/>
+      <c r="I52" s="166" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="338"/>
-      <c r="B53" s="339"/>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="338"/>
-      <c r="G53" s="339"/>
-      <c r="H53" s="339"/>
-      <c r="I53" s="340"/>
+      <c r="A53" s="326"/>
+      <c r="B53" s="327"/>
+      <c r="C53" s="327"/>
+      <c r="D53" s="327"/>
+      <c r="E53" s="328"/>
+      <c r="F53" s="326"/>
+      <c r="G53" s="327"/>
+      <c r="H53" s="327"/>
+      <c r="I53" s="328"/>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1"/>
     <row r="55" spans="1:9" ht="21" customHeight="1"/>
@@ -9999,10 +9993,10 @@
     <row r="91" spans="4:4" ht="15" customHeight="1"/>
     <row r="92" spans="4:4" ht="15" customHeight="1"/>
     <row r="94" spans="4:4">
-      <c r="D94" s="118"/>
+      <c r="D94" s="117"/>
     </row>
     <row r="95" spans="4:4">
-      <c r="D95" s="118"/>
+      <c r="D95" s="117"/>
     </row>
     <row r="105" ht="15" customHeight="1"/>
     <row r="106" ht="15" customHeight="1"/>
@@ -10021,6 +10015,29 @@
     <row r="166" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="F52:H52"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="F53:I53"/>
     <mergeCell ref="D10:E10"/>
@@ -10033,29 +10050,6 @@
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.47244094488188981" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
